--- a/data/EMPAE (TRY).xlsx
+++ b/data/EMPAE (TRY).xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:H108"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -412,6 +412,7 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -419,21 +420,24 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -447,22 +451,25 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B3">
-        <v>204310994</v>
+        <v>251155812</v>
       </c>
       <c r="C3">
-        <v>86895461</v>
+        <v>218640144.25651067</v>
       </c>
       <c r="D3">
-        <v>137811296.08175033</v>
+        <v>92990035</v>
       </c>
       <c r="E3">
-        <v>236450567.22610682</v>
+        <v>147476555.54693547</v>
       </c>
       <c r="F3">
-        <v>496538925.0880824</v>
+        <v>253033794.78370005</v>
       </c>
       <c r="G3">
-        <v>109242480.16351771</v>
+        <v>531363193.3591938</v>
+      </c>
+      <c r="H3">
+        <v>116904093.87313989</v>
       </c>
     </row>
     <row r="4">
@@ -475,15 +482,18 @@
         <v xml:space="preserve">    Finansal Yatırımlar</v>
       </c>
       <c r="B5">
-        <v>262267593</v>
+        <v>286444491</v>
       </c>
       <c r="C5">
-        <v>6194551</v>
+        <v>280661472.22272253</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>6629018</v>
       </c>
       <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>0</v>
       </c>
     </row>
@@ -497,29 +507,32 @@
         <v xml:space="preserve">    Ticari Alacaklar</v>
       </c>
       <c r="B7">
-        <v>1225504428</v>
+        <v>1672847236</v>
       </c>
       <c r="C7">
-        <v>1218719008</v>
+        <v>1311453973.5679257</v>
       </c>
       <c r="D7">
-        <v>983878407.739683</v>
+        <v>1304196129</v>
       </c>
       <c r="E7">
-        <v>925425955.3337545</v>
+        <v>1052881750.4508364</v>
       </c>
       <c r="F7">
-        <v>1073707614.1845145</v>
+        <v>990329792.8886358</v>
       </c>
       <c r="G7">
-        <v>1103931788.377686</v>
+        <v>1149011039.780934</v>
+      </c>
+      <c r="H7">
+        <v>1181354956.6512563</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklar</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>0</v>
       </c>
     </row>
@@ -533,22 +546,25 @@
         <v xml:space="preserve">    Diğer Alacaklar</v>
       </c>
       <c r="B10">
-        <v>4603371</v>
+        <v>5399300</v>
       </c>
       <c r="C10">
-        <v>5916409</v>
+        <v>4926223.889382271</v>
       </c>
       <c r="D10">
-        <v>189481.67137657342</v>
+        <v>6331368</v>
       </c>
       <c r="E10">
-        <v>1342111.0360997987</v>
+        <v>202770.7817022258</v>
       </c>
       <c r="F10">
-        <v>1048558.0505425641</v>
+        <v>1436238.6712342803</v>
       </c>
       <c r="G10">
-        <v>1238818.820724728</v>
+        <v>1122097.6362728274</v>
+      </c>
+      <c r="H10">
+        <v>1325702.1581077275</v>
       </c>
     </row>
     <row r="11">
@@ -565,7 +581,7 @@
       <c r="A13" t="str">
         <v xml:space="preserve">    Türev Araçlar</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>0</v>
       </c>
     </row>
@@ -574,22 +590,25 @@
         <v xml:space="preserve">    Stoklar</v>
       </c>
       <c r="B14">
-        <v>442275313</v>
+        <v>541497569</v>
       </c>
       <c r="C14">
-        <v>753670414</v>
+        <v>473293856.30326587</v>
       </c>
       <c r="D14">
-        <v>396044114.5938979</v>
+        <v>806530488</v>
       </c>
       <c r="E14">
-        <v>485875955.44909745</v>
+        <v>423820278.34856445</v>
       </c>
       <c r="F14">
-        <v>487281783.1222612</v>
+        <v>519952386.85080564</v>
       </c>
       <c r="G14">
-        <v>519587259.25135535</v>
+        <v>521456810.86266434</v>
+      </c>
+      <c r="H14">
+        <v>556027999.7294779</v>
       </c>
     </row>
     <row r="15">
@@ -607,22 +626,25 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B17">
-        <v>14959001</v>
+        <v>20247923</v>
       </c>
       <c r="C17">
-        <v>15041100</v>
+        <v>16008135.796027146</v>
       </c>
       <c r="D17">
-        <v>21001643.80183103</v>
+        <v>16096035</v>
       </c>
       <c r="E17">
-        <v>11017934.977850633</v>
+        <v>22474573.39694696</v>
       </c>
       <c r="F17">
-        <v>9927063.49895699</v>
+        <v>11790666.991547784</v>
       </c>
       <c r="G17">
-        <v>13280605.173435558</v>
+        <v>10623288.316317907</v>
+      </c>
+      <c r="H17">
+        <v>14212027.331890482</v>
       </c>
     </row>
     <row r="18">
@@ -634,7 +656,13 @@
       <c r="A19" t="str">
         <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Varlıklar</v>
       </c>
+      <c r="B19">
+        <v>139592</v>
+      </c>
       <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
         <v>0</v>
       </c>
     </row>
@@ -647,24 +675,30 @@
       <c r="A21" t="str">
         <v xml:space="preserve">    Diğer Dönen Varlıklar</v>
       </c>
+      <c r="B21">
+        <v>2097783</v>
+      </c>
       <c r="D21">
-        <v>2611077.0190815255</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>352394.7529760634</v>
+        <v>2794202.333119894</v>
       </c>
       <c r="F21">
-        <v>1540815.3446086508</v>
+        <v>377109.61176139134</v>
       </c>
       <c r="G21">
-        <v>1347702.280494156</v>
+        <v>1648878.91063699</v>
+      </c>
+      <c r="H21">
+        <v>1442222.0520451812</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
         <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlıklar</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>0</v>
       </c>
     </row>
@@ -678,22 +712,25 @@
         <v xml:space="preserve">    Toplam Dönen Varlıklar</v>
       </c>
       <c r="B24">
-        <v>2153920700</v>
+        <v>2779829706</v>
       </c>
       <c r="C24">
-        <v>2086436943</v>
+        <v>2304983806.0358343</v>
       </c>
       <c r="D24">
-        <v>1541536020.9076204</v>
+        <v>2232773073</v>
       </c>
       <c r="E24">
-        <v>1660464918.7758853</v>
+        <v>1649650130.8581054</v>
       </c>
       <c r="F24">
-        <v>2070044759.2889662</v>
+        <v>1776919989.797685</v>
       </c>
       <c r="G24">
-        <v>1748628654.0672135</v>
+        <v>2215225308.8660197</v>
+      </c>
+      <c r="H24">
+        <v>1871267001.7959175</v>
       </c>
     </row>
     <row r="25">
@@ -706,15 +743,18 @@
         <v xml:space="preserve">    Finansal Yatırımlar</v>
       </c>
       <c r="B26">
-        <v>7246649</v>
+        <v>7754882</v>
       </c>
       <c r="C26">
-        <v>7246635</v>
+        <v>7754885.587489721</v>
       </c>
       <c r="D26">
-        <v>7678352.156972228</v>
+        <v>7754892</v>
       </c>
       <c r="E26">
+        <v>8216865.820018955</v>
+      </c>
+      <c r="F26">
         <v>0</v>
       </c>
     </row>
@@ -727,7 +767,7 @@
       <c r="A28" t="str">
         <v xml:space="preserve">    Ticari Alacaklar</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>0</v>
       </c>
     </row>
@@ -735,7 +775,7 @@
       <c r="A29" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklar</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>0</v>
       </c>
     </row>
@@ -743,7 +783,7 @@
       <c r="A30" t="str">
         <v xml:space="preserve">    Diğer Alacaklar</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>0</v>
       </c>
     </row>
@@ -761,7 +801,7 @@
       <c r="A33" t="str">
         <v xml:space="preserve">    Türev Araçlar</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>0</v>
       </c>
     </row>
@@ -774,7 +814,7 @@
       <c r="A35" t="str">
         <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımlar</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>0</v>
       </c>
     </row>
@@ -787,7 +827,7 @@
       <c r="A37" t="str">
         <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkuller</v>
       </c>
-      <c r="D37">
+      <c r="E37">
         <v>0</v>
       </c>
     </row>
@@ -801,22 +841,25 @@
         <v xml:space="preserve">    Maddi Duran Varlıklar</v>
       </c>
       <c r="B39">
-        <v>49419086</v>
+        <v>52827121</v>
       </c>
       <c r="C39">
-        <v>51934747</v>
+        <v>52885044.90397079</v>
       </c>
       <c r="D39">
-        <v>49223924.71446013</v>
+        <v>55577287</v>
       </c>
       <c r="E39">
-        <v>8623856.78372279</v>
+        <v>52676196.17396205</v>
       </c>
       <c r="F39">
-        <v>5270650.737966971</v>
+        <v>9228682.482160697</v>
       </c>
       <c r="G39">
-        <v>6475970.510895395</v>
+        <v>5640302.634300644</v>
+      </c>
+      <c r="H39">
+        <v>6930156.321901495</v>
       </c>
     </row>
     <row r="40">
@@ -824,22 +867,25 @@
         <v xml:space="preserve">    Kullanım Hakkı Varlıkları</v>
       </c>
       <c r="B40">
-        <v>24765525</v>
+        <v>22202241</v>
       </c>
       <c r="C40">
-        <v>29649063</v>
+        <v>26502430.694396317</v>
       </c>
       <c r="D40">
-        <v>34683925.02896237</v>
+        <v>31728555</v>
       </c>
       <c r="E40">
-        <v>19484946.407112386</v>
+        <v>37116447.93678765</v>
       </c>
       <c r="F40">
-        <v>7407771.581959492</v>
+        <v>20851503.924852088</v>
       </c>
       <c r="G40">
-        <v>16463384.455890514</v>
+        <v>7927308.342980817</v>
+      </c>
+      <c r="H40">
+        <v>17618027.703327104</v>
       </c>
     </row>
     <row r="41">
@@ -847,29 +893,32 @@
         <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar</v>
       </c>
       <c r="B41">
-        <v>1098686</v>
+        <v>16785917</v>
       </c>
       <c r="C41">
-        <v>1059345</v>
+        <v>1175741.260074378</v>
       </c>
       <c r="D41">
-        <v>763140.4851403154</v>
+        <v>1133644</v>
       </c>
       <c r="E41">
-        <v>689432.0159368445</v>
+        <v>816662.5911430988</v>
       </c>
       <c r="F41">
-        <v>944330.4764319682</v>
+        <v>737784.6510770177</v>
       </c>
       <c r="G41">
-        <v>834478.6452657611</v>
+        <v>1010560.1639474427</v>
+      </c>
+      <c r="H41">
+        <v>893003.9828394335</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>0</v>
       </c>
     </row>
@@ -878,22 +927,25 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Varlığı</v>
       </c>
       <c r="B43">
-        <v>12292961</v>
+        <v>10673912</v>
       </c>
       <c r="C43">
-        <v>11211382</v>
+        <v>13155115.707477102</v>
       </c>
       <c r="D43">
-        <v>5867108.095592609</v>
+        <v>11997713</v>
       </c>
       <c r="E43">
-        <v>7484571.136678363</v>
+        <v>6278591.941013755</v>
       </c>
       <c r="F43">
-        <v>4827869.519322001</v>
+        <v>8009494.158799274</v>
       </c>
       <c r="G43">
-        <v>2488652.8660878176</v>
+        <v>5166467.391158467</v>
+      </c>
+      <c r="H43">
+        <v>2663192.082780524</v>
       </c>
     </row>
     <row r="44">
@@ -910,7 +962,7 @@
       <c r="A46" t="str">
         <v xml:space="preserve">    Diğer Duran Varlıklar</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>0</v>
       </c>
     </row>
@@ -919,22 +971,25 @@
         <v xml:space="preserve">    Toplam Duran Varlıklar</v>
       </c>
       <c r="B47">
-        <v>94822907</v>
+        <v>110244073</v>
       </c>
       <c r="C47">
-        <v>101101172</v>
+        <v>101473218.15340832</v>
       </c>
       <c r="D47">
-        <v>98216450.48112765</v>
+        <v>108192091</v>
       </c>
       <c r="E47">
-        <v>36282806.34345038</v>
+        <v>105104764.46292551</v>
       </c>
       <c r="F47">
-        <v>18450622.315680433</v>
+        <v>38827465.216889076</v>
       </c>
       <c r="G47">
-        <v>26262486.478139486</v>
+        <v>19744638.532387372</v>
+      </c>
+      <c r="H47">
+        <v>28104380.090848554</v>
       </c>
     </row>
     <row r="48">
@@ -942,22 +997,25 @@
         <v xml:space="preserve">    Toplam Varlıklar</v>
       </c>
       <c r="B48">
-        <v>2248743607</v>
+        <v>2890073779</v>
       </c>
       <c r="C48">
-        <v>2187538115</v>
+        <v>2406457024.1892424</v>
       </c>
       <c r="D48">
-        <v>1639752471.388748</v>
+        <v>2340965164</v>
       </c>
       <c r="E48">
-        <v>1696747725.1193357</v>
+        <v>1754754895.3210309</v>
       </c>
       <c r="F48">
-        <v>2088495381.6046467</v>
+        <v>1815747455.0145738</v>
       </c>
       <c r="G48">
-        <v>1774891140.5453532</v>
+        <v>2234969947.398407</v>
+      </c>
+      <c r="H48">
+        <v>1899371381.8867662</v>
       </c>
     </row>
     <row r="49">
@@ -970,22 +1028,25 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B50">
-        <v>54751011</v>
+        <v>123366987</v>
       </c>
       <c r="C50">
-        <v>161340516</v>
+        <v>58590919.210298605</v>
       </c>
       <c r="D50">
-        <v>170900178.06830645</v>
+        <v>172656432</v>
       </c>
       <c r="E50">
-        <v>58893095.50454627</v>
+        <v>182886093.66913405</v>
       </c>
       <c r="F50">
-        <v>164819215.05353355</v>
+        <v>63023504.73037421</v>
       </c>
       <c r="G50">
-        <v>74907990.85266103</v>
+        <v>176378648.30489463</v>
+      </c>
+      <c r="H50">
+        <v>80161588.98424815</v>
       </c>
     </row>
     <row r="51">
@@ -998,22 +1059,25 @@
         <v xml:space="preserve">    Ticari Borçlar</v>
       </c>
       <c r="B52">
-        <v>341249130</v>
+        <v>749759748</v>
       </c>
       <c r="C52">
-        <v>755598887</v>
+        <v>365182301.49968714</v>
       </c>
       <c r="D52">
-        <v>274963833.31155676</v>
+        <v>808594218</v>
       </c>
       <c r="E52">
-        <v>413947953.7033413</v>
+        <v>294248150.8389212</v>
       </c>
       <c r="F52">
-        <v>615424840.4713948</v>
+        <v>442979785.573291</v>
       </c>
       <c r="G52">
-        <v>618358467.6972569</v>
+        <v>658587055.2795893</v>
+      </c>
+      <c r="H52">
+        <v>661726429.5604335</v>
       </c>
     </row>
     <row r="53">
@@ -1026,22 +1090,25 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
       </c>
       <c r="B54">
-        <v>8473295</v>
+        <v>10132507</v>
       </c>
       <c r="C54">
-        <v>8758236</v>
+        <v>9067561.196085075</v>
       </c>
       <c r="D54">
-        <v>8987679.419602888</v>
+        <v>9372511</v>
       </c>
       <c r="E54">
-        <v>7626943.740445719</v>
+        <v>9618021.4601337</v>
       </c>
       <c r="F54">
-        <v>7062113.612723294</v>
+        <v>8161851.924852087</v>
       </c>
       <c r="G54">
-        <v>13987443.665229505</v>
+        <v>7557407.992649131</v>
+      </c>
+      <c r="H54">
+        <v>14968439.244858235</v>
       </c>
     </row>
     <row r="55">
@@ -1049,29 +1116,32 @@
         <v xml:space="preserve">    Diğer Borçlar</v>
       </c>
       <c r="B55">
-        <v>3602585</v>
+        <v>6302126</v>
       </c>
       <c r="C55">
-        <v>936269</v>
+        <v>3855248.7493469957</v>
       </c>
       <c r="D55">
-        <v>954861.5153719403</v>
+        <v>1001932</v>
       </c>
       <c r="E55">
-        <v>524559.0826809187</v>
+        <v>1021829.7869272343</v>
       </c>
       <c r="F55">
-        <v>296297.4381294698</v>
+        <v>561348.5170965346</v>
       </c>
       <c r="G55">
-        <v>1147757.7963442018</v>
+        <v>317077.9670107318</v>
+      </c>
+      <c r="H55">
+        <v>1228254.658504726</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülükler</v>
       </c>
-      <c r="D56">
+      <c r="E56">
         <v>0</v>
       </c>
     </row>
@@ -1084,7 +1154,7 @@
       <c r="A58" t="str">
         <v xml:space="preserve">    Türev Araçlar</v>
       </c>
-      <c r="D58">
+      <c r="E58">
         <v>0</v>
       </c>
     </row>
@@ -1092,7 +1162,7 @@
       <c r="A59" t="str">
         <v xml:space="preserve">    Devlet Teşvik ve Yardımları</v>
       </c>
-      <c r="D59">
+      <c r="E59">
         <v>0</v>
       </c>
     </row>
@@ -1101,22 +1171,25 @@
         <v xml:space="preserve">    Ertelenmiş Gelirler</v>
       </c>
       <c r="B60">
-        <v>76286</v>
+        <v>13150309</v>
       </c>
       <c r="C60">
-        <v>3776153</v>
+        <v>81636.24344538295</v>
       </c>
       <c r="D60">
-        <v>7535148.734563316</v>
+        <v>4041000</v>
       </c>
       <c r="E60">
-        <v>12014159.15692954</v>
+        <v>8063618.966677766</v>
       </c>
       <c r="F60">
-        <v>42505753.51300987</v>
+        <v>12856760.371846428</v>
       </c>
       <c r="G60">
-        <v>14276909.683323516</v>
+        <v>45486852.65471403</v>
+      </c>
+      <c r="H60">
+        <v>15278206.67692032</v>
       </c>
     </row>
     <row r="61">
@@ -1124,22 +1197,25 @@
         <v xml:space="preserve">    Dönem Karı Vergi Yükümlülüğü</v>
       </c>
       <c r="B61">
-        <v>27401090</v>
+        <v>33356111</v>
       </c>
       <c r="C61">
-        <v>39101756</v>
+        <v>29322838.44884839</v>
       </c>
       <c r="D61">
-        <v>22620309.604208466</v>
+        <v>41844231</v>
       </c>
       <c r="E61">
-        <v>15023240.12135338</v>
+        <v>24206762.73050227</v>
       </c>
       <c r="F61">
-        <v>61732642.14794514</v>
+        <v>16076880.264861822</v>
       </c>
       <c r="G61">
-        <v>47494410.09854662</v>
+        <v>66062200.17980177</v>
+      </c>
+      <c r="H61">
+        <v>50825383.75455268</v>
       </c>
     </row>
     <row r="62">
@@ -1147,22 +1223,25 @@
         <v xml:space="preserve">    Kısa Vadeli Karşılıklar</v>
       </c>
       <c r="B62">
-        <v>12626883</v>
+        <v>35641851</v>
       </c>
       <c r="C62">
-        <v>8962460</v>
+        <v>13512456.997933662</v>
       </c>
       <c r="D62">
-        <v>7126319.93759587</v>
+        <v>9591059</v>
       </c>
       <c r="E62">
-        <v>7633535.268476068</v>
+        <v>7626117.3648541365</v>
       </c>
       <c r="F62">
-        <v>6074929.400717727</v>
+        <v>8168905.74320621</v>
       </c>
       <c r="G62">
-        <v>8192261.35513266</v>
+        <v>6500988.588607433</v>
+      </c>
+      <c r="H62">
+        <v>8766817.533437492</v>
       </c>
     </row>
     <row r="63">
@@ -1170,22 +1249,25 @@
         <v xml:space="preserve">    Diğer Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B63">
-        <v>3565280</v>
+        <v>765939</v>
       </c>
       <c r="C63">
-        <v>10417916</v>
+        <v>3815327.3999286224</v>
       </c>
       <c r="D63">
-        <v>56504.47100205756</v>
+        <v>11148599</v>
       </c>
       <c r="E63">
-        <v>20580295.503294088</v>
+        <v>60467.356401915844</v>
       </c>
       <c r="F63">
-        <v>26137681.011847336</v>
+        <v>22023674.250646725</v>
       </c>
       <c r="G63">
-        <v>704261.3033720655</v>
+        <v>27970821.516148865</v>
+      </c>
+      <c r="H63">
+        <v>753653.9759752069</v>
       </c>
     </row>
     <row r="64">
@@ -1203,22 +1285,25 @@
         <v xml:space="preserve">    Toplam Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B66">
-        <v>451745560</v>
+        <v>972475578</v>
       </c>
       <c r="C66">
-        <v>988892193</v>
+        <v>483428289.7455739</v>
       </c>
       <c r="D66">
-        <v>493144835.06220776</v>
+        <v>1058249982</v>
       </c>
       <c r="E66">
-        <v>536243782.0810673</v>
+        <v>527731062.1735523</v>
       </c>
       <c r="F66">
-        <v>924053472.6493012</v>
+        <v>573852711.376175</v>
       </c>
       <c r="G66">
-        <v>779069502.4518665</v>
+        <v>988861052.4834158</v>
+      </c>
+      <c r="H66">
+        <v>833708774.3889303</v>
       </c>
     </row>
     <row r="67">
@@ -1231,19 +1316,22 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B68">
-        <v>15935437</v>
+        <v>12285549</v>
       </c>
       <c r="C68">
-        <v>21296438</v>
+        <v>17053053.172804482</v>
       </c>
       <c r="D68">
-        <v>24654547.589825463</v>
+        <v>22790104</v>
       </c>
       <c r="E68">
-        <v>661808.1214216803</v>
-      </c>
-      <c r="G68">
-        <v>6203436.686758474</v>
+        <v>26383669.992905263</v>
+      </c>
+      <c r="F68">
+        <v>708223.3819378634</v>
+      </c>
+      <c r="H68">
+        <v>6638508.606536384</v>
       </c>
     </row>
     <row r="69">
@@ -1255,7 +1343,7 @@
       <c r="A70" t="str">
         <v xml:space="preserve">    Ticari Borçlar</v>
       </c>
-      <c r="D70">
+      <c r="E70">
         <v>0</v>
       </c>
     </row>
@@ -1273,7 +1361,7 @@
       <c r="A73" t="str">
         <v xml:space="preserve">    Diğer Borçlar</v>
       </c>
-      <c r="D73">
+      <c r="E73">
         <v>0</v>
       </c>
     </row>
@@ -1281,7 +1369,7 @@
       <c r="A74" t="str">
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülükler</v>
       </c>
-      <c r="D74">
+      <c r="E74">
         <v>0</v>
       </c>
     </row>
@@ -1289,7 +1377,7 @@
       <c r="A75" t="str">
         <v xml:space="preserve">    Devlet Teşvik ve Yardımları</v>
       </c>
-      <c r="D75">
+      <c r="E75">
         <v>0</v>
       </c>
     </row>
@@ -1307,7 +1395,7 @@
       <c r="A78" t="str">
         <v xml:space="preserve">    Devlet Teşvik ve Yardımları</v>
       </c>
-      <c r="D78">
+      <c r="E78">
         <v>0</v>
       </c>
     </row>
@@ -1315,7 +1403,7 @@
       <c r="A79" t="str">
         <v xml:space="preserve">    Ertelenmiş Gelirler</v>
       </c>
-      <c r="D79">
+      <c r="E79">
         <v>0</v>
       </c>
     </row>
@@ -1324,22 +1412,25 @@
         <v xml:space="preserve">    Uzun vadeli Karşılıklar</v>
       </c>
       <c r="B80">
-        <v>7000698</v>
+        <v>7508953</v>
       </c>
       <c r="C80">
-        <v>4551532</v>
+        <v>7491685.05644031</v>
       </c>
       <c r="D80">
-        <v>6640205.19936708</v>
+        <v>4870762</v>
       </c>
       <c r="E80">
-        <v>3171432.8307820153</v>
+        <v>7105909.448428657</v>
       </c>
       <c r="F80">
-        <v>5526877.40786654</v>
+        <v>3393858.14755526</v>
       </c>
       <c r="G80">
-        <v>13543001.909723468</v>
+        <v>5914499.5092334105</v>
+      </c>
+      <c r="H80">
+        <v>14492827.004738368</v>
       </c>
     </row>
     <row r="81">
@@ -1351,7 +1442,7 @@
       <c r="A82" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Yükümlülüğü</v>
       </c>
-      <c r="D82">
+      <c r="E82">
         <v>0</v>
       </c>
     </row>
@@ -1359,7 +1450,7 @@
       <c r="A83" t="str">
         <v xml:space="preserve">    Diğer Uzun Vadeli Yükümlülükler</v>
       </c>
-      <c r="D83">
+      <c r="E83">
         <v>0</v>
       </c>
     </row>
@@ -1368,22 +1459,25 @@
         <v xml:space="preserve">    Toplam Uzun Vadeli Yükümlülükler</v>
       </c>
       <c r="B84">
-        <v>22936135</v>
+        <v>19794502</v>
       </c>
       <c r="C84">
-        <v>25847970</v>
+        <v>24544738.229244795</v>
       </c>
       <c r="D84">
-        <v>31294752.789192542</v>
+        <v>27660866</v>
       </c>
       <c r="E84">
-        <v>3833240.9522036957</v>
+        <v>33489579.44133392</v>
       </c>
       <c r="F84">
-        <v>5526877.40786654</v>
+        <v>4102081.5294931238</v>
       </c>
       <c r="G84">
-        <v>19746438.59648194</v>
+        <v>5914499.5092334105</v>
+      </c>
+      <c r="H84">
+        <v>21131335.611274753</v>
       </c>
     </row>
     <row r="85">
@@ -1396,22 +1490,25 @@
         <v xml:space="preserve">    Ana Ortaklığa Ait Özkaynaklar</v>
       </c>
       <c r="B86">
-        <v>1774061912</v>
+        <v>1897803699</v>
       </c>
       <c r="C86">
-        <v>1172797952</v>
+        <v>1898483996.214424</v>
       </c>
       <c r="D86">
-        <v>1115312883.5373478</v>
+        <v>1255054316</v>
       </c>
       <c r="E86">
-        <v>1156670702.0860646</v>
+        <v>1193534253.7061448</v>
       </c>
       <c r="F86">
-        <v>1158915031.547479</v>
+        <v>1237792662.1089056</v>
       </c>
       <c r="G86">
-        <v>976075199.4970047</v>
+        <v>1240194395.405758</v>
+      </c>
+      <c r="H86">
+        <v>1044531271.8865612</v>
       </c>
     </row>
     <row r="87">
@@ -1422,18 +1519,21 @@
         <v>170000000</v>
       </c>
       <c r="C87">
+        <v>170000000</v>
+      </c>
+      <c r="D87">
         <v>141000000</v>
       </c>
-      <c r="D87">
+      <c r="E87">
         <v>147139986</v>
-      </c>
-      <c r="E87">
-        <v>141000000</v>
       </c>
       <c r="F87">
         <v>141000000</v>
       </c>
       <c r="G87">
+        <v>141000000</v>
+      </c>
+      <c r="H87">
         <v>245233</v>
       </c>
     </row>
@@ -1442,22 +1542,25 @@
         <v xml:space="preserve">    Sermaye Düzeltme Farkları</v>
       </c>
       <c r="B88">
-        <v>204597755</v>
+        <v>230869520</v>
       </c>
       <c r="C88">
-        <v>204033151</v>
+        <v>230869799.45565262</v>
       </c>
       <c r="D88">
-        <v>197893739.12159526</v>
+        <v>228232692</v>
       </c>
       <c r="E88">
-        <v>204033791.1469178</v>
+        <v>222092339.47117284</v>
       </c>
       <c r="F88">
-        <v>204033791.1469178</v>
+        <v>228232396.12711632</v>
       </c>
       <c r="G88">
-        <v>7615910.262334691</v>
+        <v>228232396.12711632</v>
+      </c>
+      <c r="H88">
+        <v>8167243.799451888</v>
       </c>
     </row>
     <row r="89">
@@ -1490,12 +1593,15 @@
         <v xml:space="preserve">    Paylara İlişkin Primler (İskontolar)</v>
       </c>
       <c r="B94">
-        <v>578275441</v>
+        <v>618832219</v>
       </c>
       <c r="C94">
-        <v>0</v>
+        <v>618832219.2795819</v>
       </c>
       <c r="D94">
+        <v>0</v>
+      </c>
+      <c r="E94">
         <v>0</v>
       </c>
     </row>
@@ -1514,22 +1620,25 @@
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
       <c r="B97">
-        <v>-5510446</v>
+        <v>-6226693</v>
       </c>
       <c r="C97">
-        <v>-5563287</v>
+        <v>-5896915.70076602</v>
       </c>
       <c r="D97">
-        <v>-7234796.241209834</v>
+        <v>-5953478</v>
       </c>
       <c r="E97">
-        <v>-5592866.416446824</v>
+        <v>-7742201.547140333</v>
       </c>
       <c r="F97">
-        <v>-5333852.377515389</v>
+        <v>-5985116.591911483</v>
       </c>
       <c r="G97">
-        <v>-4408894.831129211</v>
+        <v>-5707936.858566197</v>
+      </c>
+      <c r="H97">
+        <v>-4718108.326025153</v>
       </c>
     </row>
     <row r="98">
@@ -1537,12 +1646,15 @@
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
       <c r="B98">
-        <v>-1830779</v>
+        <v>-570072</v>
       </c>
       <c r="C98">
-        <v>-94389</v>
-      </c>
-      <c r="E98">
+        <v>-1959178.881297941</v>
+      </c>
+      <c r="D98">
+        <v>-101009</v>
+      </c>
+      <c r="F98">
         <v>0</v>
       </c>
     </row>
@@ -1551,33 +1663,36 @@
         <v xml:space="preserve">    Kardan Ayrılan Kısıtlanmış Yedekler</v>
       </c>
       <c r="B99">
-        <v>150507105</v>
+        <v>161913201</v>
       </c>
       <c r="C99">
-        <v>150507105</v>
+        <v>161062772.5144825</v>
       </c>
       <c r="D99">
-        <v>150506660.49943224</v>
+        <v>161063201</v>
       </c>
       <c r="E99">
-        <v>143577557.09974474</v>
+        <v>161062296.8393054</v>
       </c>
       <c r="F99">
-        <v>105523277.04792722</v>
+        <v>153647227.59992832</v>
       </c>
       <c r="G99">
-        <v>90300512.80364385</v>
+        <v>112924048.11156932</v>
+      </c>
+      <c r="H99">
+        <v>96633650.29600699</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
         <v xml:space="preserve">    Diğer Özkaynak Payları</v>
       </c>
-      <c r="D100">
-        <v>0</v>
-      </c>
-      <c r="G100">
-        <v>-11701616.18819706</v>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>-12522297.509950569</v>
       </c>
     </row>
     <row r="101">
@@ -1595,22 +1710,25 @@
         <v xml:space="preserve">    Geçmiş Yıllar Kar/Zararları</v>
       </c>
       <c r="B103">
-        <v>682915372</v>
+        <v>712962910</v>
       </c>
       <c r="C103">
-        <v>591898124</v>
+        <v>730810968.7385137</v>
       </c>
       <c r="D103">
-        <v>591899368.81291</v>
+        <v>633411998</v>
       </c>
       <c r="E103">
-        <v>576432122.7031791</v>
+        <v>633411647.8459904</v>
       </c>
       <c r="F103">
-        <v>377663223.8221619</v>
+        <v>616859621.6702355</v>
       </c>
       <c r="G103">
-        <v>633419736.2035306</v>
+        <v>404150261.91324955</v>
+      </c>
+      <c r="H103">
+        <v>677844005.2935226</v>
       </c>
     </row>
     <row r="104">
@@ -1618,29 +1736,32 @@
         <v xml:space="preserve">    Dönem Net Kar/Zararı</v>
       </c>
       <c r="B104">
-        <v>-4892536</v>
+        <v>10022614</v>
       </c>
       <c r="C104">
-        <v>91017248</v>
+        <v>-5235669.191742916</v>
       </c>
       <c r="D104">
-        <v>35107925.344620034</v>
+        <v>97400912</v>
       </c>
       <c r="E104">
-        <v>97220097.55266985</v>
+        <v>37570185.09681634</v>
       </c>
       <c r="F104">
-        <v>336028591.9079875</v>
+        <v>104038533.30353715</v>
       </c>
       <c r="G104">
-        <v>260604318.24682188</v>
+        <v>359595626.1123889</v>
+      </c>
+      <c r="H104">
+        <v>278881545.33355534</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
-      <c r="D105">
+      <c r="E105">
         <v>0</v>
       </c>
     </row>
@@ -1649,22 +1770,25 @@
         <v xml:space="preserve">    Toplam Özkaynaklar</v>
       </c>
       <c r="B106">
-        <v>1774061912</v>
+        <v>1897803699</v>
       </c>
       <c r="C106">
-        <v>1172797952</v>
+        <v>1898483996.214424</v>
       </c>
       <c r="D106">
-        <v>1115312883.5373478</v>
+        <v>1255054316</v>
       </c>
       <c r="E106">
-        <v>1156670702.0860646</v>
+        <v>1193534253.7061448</v>
       </c>
       <c r="F106">
-        <v>1158915031.547479</v>
+        <v>1237792662.1089056</v>
       </c>
       <c r="G106">
-        <v>976075199.4970047</v>
+        <v>1240194395.405758</v>
+      </c>
+      <c r="H106">
+        <v>1044531271.8865612</v>
       </c>
     </row>
     <row r="107">
@@ -1672,42 +1796,51 @@
         <v xml:space="preserve">    Toplam Kaynaklar</v>
       </c>
       <c r="B107">
-        <v>2248743607</v>
+        <v>2890073779</v>
       </c>
       <c r="C107">
-        <v>2187538115</v>
+        <v>2406457024.1892424</v>
       </c>
       <c r="D107">
-        <v>1639752471.388748</v>
+        <v>2340965164</v>
       </c>
       <c r="E107">
-        <v>1696747725.1193357</v>
+        <v>1754754895.3210309</v>
       </c>
       <c r="F107">
-        <v>2088495381.6046467</v>
+        <v>1815747455.0145738</v>
       </c>
       <c r="G107">
-        <v>1774891140.5453532</v>
+        <v>2234969947.398407</v>
+      </c>
+      <c r="H107">
+        <v>1899371381.8867662</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
         <v xml:space="preserve">    Hedge Dahil Net Yabancı Para Pozisyonu</v>
       </c>
-      <c r="D108">
+      <c r="B108">
+        <v>584871013</v>
+      </c>
+      <c r="C108">
+        <v>716622639.709978</v>
+      </c>
+      <c r="E108">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H108"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -1718,6 +1851,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1725,27 +1860,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -1759,28 +1900,34 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>1071319927</v>
+        <v>2687694777</v>
       </c>
       <c r="C3">
-        <v>3988500061.4965496</v>
+        <v>1146455895</v>
       </c>
       <c r="D3">
-        <v>2842821455.378372</v>
+        <v>4268229583.4393883</v>
       </c>
       <c r="E3">
-        <v>834989957</v>
+        <v>3042199937.118562</v>
       </c>
       <c r="F3">
-        <v>3879530777.6112375</v>
+        <v>2094941924</v>
       </c>
       <c r="G3">
-        <v>2848616623.3829823</v>
+        <v>893551155</v>
       </c>
       <c r="H3">
-        <v>5604942822.076969</v>
+        <v>4151617846.1962457</v>
       </c>
       <c r="I3">
-        <v>4857887189.415232</v>
+        <v>3048401543.521195</v>
+      </c>
+      <c r="J3">
+        <v>5998039964.351613</v>
+      </c>
+      <c r="K3">
+        <v>5198590320.967268</v>
       </c>
     </row>
     <row r="4">
@@ -1803,28 +1950,34 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-860906166</v>
+        <v>-2157406889</v>
       </c>
       <c r="C7">
-        <v>-3162544771.469434</v>
+        <v>-921284972</v>
       </c>
       <c r="D7">
-        <v>-2237565651.3091264</v>
+        <v>-3384346732.960198</v>
       </c>
       <c r="E7">
-        <v>-672636857</v>
+        <v>-2394495113.589632</v>
       </c>
       <c r="F7">
-        <v>-3089128155.099466</v>
+        <v>-1648007146</v>
       </c>
       <c r="G7">
-        <v>-2242040642.990196</v>
+        <v>-719811580</v>
       </c>
       <c r="H7">
-        <v>-4460743739.996516</v>
+        <v>-3305781114.538535</v>
       </c>
       <c r="I7">
-        <v>-3916734455.634033</v>
+        <v>-2399283954.4030433</v>
+      </c>
+      <c r="J7">
+        <v>-4773593607.029122</v>
+      </c>
+      <c r="K7">
+        <v>-4191430767.5203757</v>
       </c>
     </row>
     <row r="8">
@@ -1832,28 +1985,34 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>210413761</v>
+        <v>530287888</v>
       </c>
       <c r="C8">
-        <v>825955290.0271153</v>
+        <v>225170923</v>
       </c>
       <c r="D8">
-        <v>605255804.0692456</v>
+        <v>883882850.4791896</v>
       </c>
       <c r="E8">
-        <v>162353100</v>
+        <v>647704823.5289297</v>
       </c>
       <c r="F8">
-        <v>790402622.5117719</v>
+        <v>446934778</v>
       </c>
       <c r="G8">
-        <v>606575980.3927863</v>
+        <v>173739575</v>
       </c>
       <c r="H8">
-        <v>1144199082.0804527</v>
+        <v>845836731.6577108</v>
       </c>
       <c r="I8">
-        <v>941152733.7811985</v>
+        <v>649117589.1181518</v>
+      </c>
+      <c r="J8">
+        <v>1224446357.322491</v>
+      </c>
+      <c r="K8">
+        <v>1007159553.446892</v>
       </c>
     </row>
     <row r="9">
@@ -1881,28 +2040,34 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>210413761</v>
+        <v>530287888</v>
       </c>
       <c r="C13">
-        <v>825955290.0271153</v>
+        <v>225170923</v>
       </c>
       <c r="D13">
-        <v>605255804.0692456</v>
+        <v>883882850.4791896</v>
       </c>
       <c r="E13">
-        <v>162353100</v>
+        <v>647704823.5289297</v>
       </c>
       <c r="F13">
-        <v>790402622.5117719</v>
+        <v>446934778</v>
       </c>
       <c r="G13">
-        <v>606575980.3927863</v>
+        <v>173739575</v>
       </c>
       <c r="H13">
-        <v>1144199082.0804527</v>
+        <v>845836731.6577108</v>
       </c>
       <c r="I13">
-        <v>941152733.7811985</v>
+        <v>649117589.1181518</v>
+      </c>
+      <c r="J13">
+        <v>1224446357.322491</v>
+      </c>
+      <c r="K13">
+        <v>1007159553.446892</v>
       </c>
     </row>
     <row r="14"/>
@@ -1911,28 +2076,34 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-21767996</v>
+        <v>-52552440</v>
       </c>
       <c r="C15">
-        <v>-78086974.77949384</v>
+        <v>-23294673</v>
       </c>
       <c r="D15">
-        <v>-59123342.31046112</v>
+        <v>-83563527.81653564</v>
       </c>
       <c r="E15">
-        <v>-17397245</v>
+        <v>-63269899.66915966</v>
       </c>
       <c r="F15">
-        <v>-41298333.03440366</v>
+        <v>-40937069</v>
       </c>
       <c r="G15">
-        <v>-29709987.688656665</v>
+        <v>-18617384</v>
       </c>
       <c r="H15">
-        <v>-38548393.7578681</v>
+        <v>-44194750.93051251</v>
       </c>
       <c r="I15">
-        <v>-38813532.745884165</v>
+        <v>-31793668.401941452</v>
+      </c>
+      <c r="J15">
+        <v>-41251947.37233307</v>
+      </c>
+      <c r="K15">
+        <v>-41535681.62203212</v>
       </c>
     </row>
     <row r="16">
@@ -1940,28 +2111,34 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-75361641</v>
+        <v>-206242974</v>
       </c>
       <c r="C16">
-        <v>-332332805.7734464</v>
+        <v>-80647055</v>
       </c>
       <c r="D16">
-        <v>-251442621.38679576</v>
+        <v>-355640639.6587609</v>
       </c>
       <c r="E16">
-        <v>-78233773</v>
+        <v>-269077301.89127374</v>
       </c>
       <c r="F16">
-        <v>-299490895.9074183</v>
+        <v>-175266152</v>
       </c>
       <c r="G16">
-        <v>-198075197.22755823</v>
+        <v>-83720622</v>
       </c>
       <c r="H16">
-        <v>-293127392.93088245</v>
+        <v>-320495394.8034219</v>
       </c>
       <c r="I16">
-        <v>-226074440.19906828</v>
+        <v>-211967006.021566</v>
+      </c>
+      <c r="J16">
+        <v>-313685593.81558794</v>
+      </c>
+      <c r="K16">
+        <v>-241929948.311221</v>
       </c>
     </row>
     <row r="17">
@@ -1969,22 +2146,28 @@
         <v xml:space="preserve">    Araştırma ve Geliştirme Giderleri (-)</v>
       </c>
       <c r="B17">
-        <v>-15857074</v>
+        <v>-19060736</v>
       </c>
       <c r="C17">
-        <v>-12683739.559232414</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
+        <v>-16969194</v>
+      </c>
+      <c r="D17">
+        <v>-13573301.135927057</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
       <c r="H17">
-        <v>-56053.29796492187</v>
-      </c>
-      <c r="I17">
-        <v>-3111197.9290582747</v>
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>-59984.54078836156</v>
+      </c>
+      <c r="K17">
+        <v>-3329398.7303485903</v>
       </c>
     </row>
     <row r="18">
@@ -1992,28 +2175,34 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>82714125</v>
+        <v>138979154</v>
       </c>
       <c r="C18">
-        <v>279254253.4044003</v>
+        <v>88515199</v>
       </c>
       <c r="D18">
-        <v>213295497.62689</v>
+        <v>298839475.3176242</v>
       </c>
       <c r="E18">
-        <v>71315819</v>
+        <v>228254767.1928387</v>
       </c>
       <c r="F18">
-        <v>217764157.4795311</v>
+        <v>163444162</v>
       </c>
       <c r="G18">
-        <v>177321171.4939938</v>
+        <v>76317484</v>
       </c>
       <c r="H18">
-        <v>647647501.0384675</v>
+        <v>233036832.10127297</v>
       </c>
       <c r="I18">
-        <v>384154777.40959114</v>
+        <v>189757417.14212537</v>
+      </c>
+      <c r="J18">
+        <v>693069620.3965372</v>
+      </c>
+      <c r="K18">
+        <v>411097094.2154036</v>
       </c>
     </row>
     <row r="19">
@@ -2021,28 +2210,34 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-62785176</v>
+        <v>-101866006</v>
       </c>
       <c r="C19">
-        <v>-157136355.56787816</v>
+        <v>-67188552</v>
       </c>
       <c r="D19">
-        <v>-125325575.26809472</v>
+        <v>-168156959.03913638</v>
       </c>
       <c r="E19">
-        <v>-45889031</v>
+        <v>-134115161.0061983</v>
       </c>
       <c r="F19">
-        <v>-97325614.82141343</v>
+        <v>-100144547</v>
       </c>
       <c r="G19">
-        <v>-74963511.54635772</v>
+        <v>-49107413</v>
       </c>
       <c r="H19">
-        <v>-376311140.7615194</v>
+        <v>-104151450.92195785</v>
       </c>
       <c r="I19">
-        <v>-226259537.7890303</v>
+        <v>-80221003.5670927</v>
+      </c>
+      <c r="J19">
+        <v>-402703351.83935666</v>
+      </c>
+      <c r="K19">
+        <v>-242128027.5382783</v>
       </c>
     </row>
     <row r="20">
@@ -2055,28 +2250,34 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>117355999</v>
+        <v>289544886</v>
       </c>
       <c r="C21">
-        <v>524969667.7514649</v>
+        <v>125586648</v>
       </c>
       <c r="D21">
-        <v>382659762.730784</v>
+        <v>561787898.146454</v>
       </c>
       <c r="E21">
-        <v>92148870</v>
+        <v>409497228.1551367</v>
       </c>
       <c r="F21">
-        <v>570051936.2280676</v>
+        <v>294031172</v>
       </c>
       <c r="G21">
-        <v>481148455.4242075</v>
+        <v>98611640</v>
       </c>
       <c r="H21">
-        <v>1083803602.3706853</v>
+        <v>610031967.1030916</v>
       </c>
       <c r="I21">
-        <v>831048802.5277486</v>
+        <v>514893328.2696771</v>
+      </c>
+      <c r="J21">
+        <v>1159815100.1509619</v>
+      </c>
+      <c r="K21">
+        <v>889333591.4604155</v>
       </c>
     </row>
     <row r="22"/>
@@ -2095,28 +2296,34 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>13858660</v>
+        <v>49357158</v>
       </c>
       <c r="C25">
-        <v>18679341.73580127</v>
+        <v>14830623</v>
       </c>
       <c r="D25">
-        <v>13141936.59026088</v>
+        <v>19989398.963681072</v>
       </c>
       <c r="E25">
-        <v>6788928</v>
+        <v>14063633.364265043</v>
       </c>
       <c r="F25">
-        <v>47163965.46403822</v>
+        <v>11028963</v>
       </c>
       <c r="G25">
-        <v>34722093.167482</v>
+        <v>7265063</v>
       </c>
       <c r="H25">
-        <v>17634597.748055562</v>
+        <v>50471763.71119023</v>
       </c>
       <c r="I25">
-        <v>4500572.091853142</v>
+        <v>37157292.96009528</v>
+      </c>
+      <c r="J25">
+        <v>18871382.885741364</v>
+      </c>
+      <c r="K25">
+        <v>4816215.281100325</v>
       </c>
     </row>
     <row r="26">
@@ -2127,15 +2334,21 @@
         <v>0</v>
       </c>
       <c r="C26">
-        <v>-633123.4200582264</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>-594804.5237188627</v>
+        <v>-677526.907307328</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>-636520.5529288221</v>
       </c>
       <c r="F26">
+        <v>-635967</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
         <v>0</v>
       </c>
     </row>
@@ -2174,28 +2387,34 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>131214659</v>
+        <v>338902044</v>
       </c>
       <c r="C33">
-        <v>543015886.0672079</v>
+        <v>140417271</v>
       </c>
       <c r="D33">
-        <v>395206894.797326</v>
+        <v>581099770.2028277</v>
       </c>
       <c r="E33">
-        <v>98937798</v>
+        <v>422924340.9664729</v>
       </c>
       <c r="F33">
-        <v>617215901.6921059</v>
+        <v>304424168</v>
       </c>
       <c r="G33">
-        <v>515870548.5916895</v>
+        <v>105876703</v>
       </c>
       <c r="H33">
-        <v>1101438200.1187408</v>
+        <v>660503730.8142818</v>
       </c>
       <c r="I33">
-        <v>835549374.6196017</v>
+        <v>552050621.2297724</v>
+      </c>
+      <c r="J33">
+        <v>1178686483.036703</v>
+      </c>
+      <c r="K33">
+        <v>894149806.7415159</v>
       </c>
     </row>
     <row r="34"/>
@@ -2209,28 +2428,34 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-11158657</v>
+        <v>-36117775</v>
       </c>
       <c r="C36">
-        <v>-46163415.52591302</v>
+        <v>-11941258</v>
       </c>
       <c r="D36">
-        <v>-32074829.869978115</v>
+        <v>-49401041.188996755</v>
       </c>
       <c r="E36">
-        <v>-5431348</v>
+        <v>-34324366.45957022</v>
       </c>
       <c r="F36">
-        <v>-29640590.673012946</v>
+        <v>-17214363</v>
       </c>
       <c r="G36">
-        <v>-23716358.56880875</v>
+        <v>-5812270</v>
       </c>
       <c r="H36">
-        <v>-39465468.98116891</v>
+        <v>-31719404.29498246</v>
       </c>
       <c r="I36">
-        <v>-13596845.560228465</v>
+        <v>-25379682.009297445</v>
+      </c>
+      <c r="J36">
+        <v>-42233340.76282561</v>
+      </c>
+      <c r="K36">
+        <v>-14550446.92661937</v>
       </c>
     </row>
     <row r="37">
@@ -2238,28 +2463,34 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>-96239172</v>
+        <v>-226776084</v>
       </c>
       <c r="C37">
-        <v>-286985996.9384183</v>
+        <v>-102988812</v>
       </c>
       <c r="D37">
-        <v>-239133758.20285326</v>
+        <v>-307113477.06631154</v>
       </c>
       <c r="E37">
-        <v>-88692832</v>
+        <v>-255905168.71585178</v>
       </c>
       <c r="F37">
-        <v>-410586857.63154584</v>
+        <v>-174590140</v>
       </c>
       <c r="G37">
-        <v>-332519744.36948436</v>
+        <v>-94913216</v>
       </c>
       <c r="H37">
-        <v>-509696226.8713128</v>
+        <v>-439382962.3401891</v>
       </c>
       <c r="I37">
-        <v>-396942536.5631682</v>
+        <v>-355840689.00904137</v>
+      </c>
+      <c r="J37">
+        <v>-545443269.5390979</v>
+      </c>
+      <c r="K37">
+        <v>-424781710.2574341</v>
       </c>
     </row>
     <row r="38">
@@ -2267,28 +2498,34 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>23816830</v>
+        <v>76008185</v>
       </c>
       <c r="C38">
-        <v>209866473.6028766</v>
+        <v>25487201</v>
       </c>
       <c r="D38">
-        <v>123998306.72449465</v>
+        <v>224585251.94751942</v>
       </c>
       <c r="E38">
-        <v>4813618</v>
+        <v>132694805.79105091</v>
       </c>
       <c r="F38">
-        <v>176988453.38754708</v>
+        <v>112619665</v>
       </c>
       <c r="G38">
-        <v>159634445.6533964</v>
+        <v>5151217</v>
       </c>
       <c r="H38">
-        <v>552276504.2662592</v>
+        <v>189401364.17911026</v>
       </c>
       <c r="I38">
-        <v>425009992.49620503</v>
+        <v>170830250.21143356</v>
+      </c>
+      <c r="J38">
+        <v>591009872.7347797</v>
+      </c>
+      <c r="K38">
+        <v>454817649.55746233</v>
       </c>
     </row>
     <row r="39"/>
@@ -2297,28 +2534,34 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>-28709366</v>
+        <v>-65985571</v>
       </c>
       <c r="C40">
-        <v>-118849056.74702251</v>
+        <v>-30722869</v>
       </c>
       <c r="D40">
-        <v>-88890380.27945256</v>
+        <v>-127184418.2399662</v>
       </c>
       <c r="E40">
-        <v>-28694480</v>
+        <v>-95124619.5166355</v>
       </c>
       <c r="F40">
-        <v>-79768355.83487721</v>
+        <v>-73644321</v>
       </c>
       <c r="G40">
-        <v>-67072454.411238894</v>
+        <v>-30706939</v>
       </c>
       <c r="H40">
-        <v>-216247912.35827166</v>
+        <v>-85362830.87557308</v>
       </c>
       <c r="I40">
-        <v>-164405674.24938315</v>
+        <v>-71776514.91486311</v>
+      </c>
+      <c r="J40">
+        <v>-231414246.62239075</v>
+      </c>
+      <c r="K40">
+        <v>-175936104.223907</v>
       </c>
     </row>
     <row r="41">
@@ -2326,28 +2569,34 @@
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
       <c r="B41">
-        <v>-29808570</v>
+        <v>-64570709</v>
       </c>
       <c r="C41">
-        <v>-124352191.4489153</v>
+        <v>-31899165</v>
       </c>
       <c r="D41">
-        <v>-88243041.60745844</v>
+        <v>-133073509.8719361</v>
       </c>
       <c r="E41">
-        <v>-30661686</v>
+        <v>-94431880.38470405</v>
       </c>
       <c r="F41">
-        <v>-83822704.58793865</v>
+        <v>-74948365</v>
       </c>
       <c r="G41">
-        <v>-71968550.09715214</v>
+        <v>-32812113</v>
       </c>
       <c r="H41">
-        <v>-219257109.96743193</v>
+        <v>-89701527.38367954</v>
       </c>
       <c r="I41">
-        <v>-180233329.48582047</v>
+        <v>-77015993.44758345</v>
+      </c>
+      <c r="J41">
+        <v>-234634491.34090623</v>
+      </c>
+      <c r="K41">
+        <v>-192873816.46535873</v>
       </c>
     </row>
     <row r="42">
@@ -2355,28 +2604,34 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>1099204</v>
+        <v>-1414862</v>
       </c>
       <c r="C42">
-        <v>5503134.701892785</v>
+        <v>1176296</v>
       </c>
       <c r="D42">
-        <v>-647338.6719941262</v>
+        <v>5889091.63196988</v>
       </c>
       <c r="E42">
-        <v>1967206</v>
+        <v>-692739.1319314603</v>
       </c>
       <c r="F42">
-        <v>4054348.7530614394</v>
+        <v>1304044</v>
       </c>
       <c r="G42">
-        <v>4896095.685913253</v>
+        <v>2105174</v>
       </c>
       <c r="H42">
-        <v>3009197.6091602705</v>
+        <v>4338696.508106448</v>
       </c>
       <c r="I42">
-        <v>15827655.236437319</v>
+        <v>5239478.532720335</v>
+      </c>
+      <c r="J42">
+        <v>3220244.718515483</v>
+      </c>
+      <c r="K42">
+        <v>16937712.241451737</v>
       </c>
     </row>
     <row r="43">
@@ -2384,28 +2639,34 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>-4892536</v>
+        <v>10022614</v>
       </c>
       <c r="C43">
-        <v>91017416.8558541</v>
+        <v>-5235668</v>
       </c>
       <c r="D43">
-        <v>35107926.445042074</v>
+        <v>97400833.70755324</v>
       </c>
       <c r="E43">
-        <v>-23880862</v>
+        <v>37570186.27441539</v>
       </c>
       <c r="F43">
-        <v>97220097.55266985</v>
+        <v>38975344</v>
       </c>
       <c r="G43">
-        <v>92561991.2421575</v>
+        <v>-25555722</v>
       </c>
       <c r="H43">
-        <v>336028591.9079875</v>
+        <v>104038533.30353715</v>
       </c>
       <c r="I43">
-        <v>260604318.24682188</v>
+        <v>99053735.29657046</v>
+      </c>
+      <c r="J43">
+        <v>359595626.1123889</v>
+      </c>
+      <c r="K43">
+        <v>278881545.33355534</v>
       </c>
     </row>
     <row r="44">
@@ -2419,28 +2680,34 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>-4892536</v>
+        <v>10022614</v>
       </c>
       <c r="C46">
-        <v>91017416.8558541</v>
+        <v>-5235668</v>
       </c>
       <c r="D46">
-        <v>35107926.445042074</v>
+        <v>97400833.70755324</v>
       </c>
       <c r="E46">
-        <v>-23880862</v>
+        <v>37570186.27441539</v>
       </c>
       <c r="F46">
-        <v>97220097.55266985</v>
+        <v>38975344</v>
       </c>
       <c r="G46">
-        <v>92561991.2421575</v>
+        <v>-25555722</v>
       </c>
       <c r="H46">
-        <v>336028591.9079875</v>
+        <v>104038533.30353715</v>
       </c>
       <c r="I46">
-        <v>260604318.24682188</v>
+        <v>99053735.29657046</v>
+      </c>
+      <c r="J46">
+        <v>359595626.1123889</v>
+      </c>
+      <c r="K46">
+        <v>278881545.33355534</v>
       </c>
     </row>
     <row r="47">
@@ -2453,10 +2720,16 @@
       <c r="C47">
         <v>0</v>
       </c>
-      <c r="E47">
+      <c r="D47">
         <v>0</v>
       </c>
       <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
         <v>0</v>
       </c>
     </row>
@@ -2465,28 +2738,34 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>-4892536</v>
+        <v>10022614</v>
       </c>
       <c r="C48">
-        <v>91017416.8558541</v>
+        <v>-5235668</v>
       </c>
       <c r="D48">
-        <v>35107926.445042074</v>
+        <v>97400833.70755324</v>
       </c>
       <c r="E48">
-        <v>-23880862</v>
+        <v>37570186.27441539</v>
       </c>
       <c r="F48">
-        <v>97220097.55266985</v>
+        <v>38975344</v>
       </c>
       <c r="G48">
-        <v>92561991.2421575</v>
+        <v>-25555722</v>
       </c>
       <c r="H48">
-        <v>336028591.9079875</v>
+        <v>104038533.30353715</v>
       </c>
       <c r="I48">
-        <v>260604318.24682188</v>
+        <v>99053735.29657046</v>
+      </c>
+      <c r="J48">
+        <v>359595626.1123889</v>
+      </c>
+      <c r="K48">
+        <v>278881545.33355534</v>
       </c>
     </row>
     <row r="49"/>
@@ -2495,40 +2774,46 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>8302570</v>
+        <v>16902436</v>
       </c>
       <c r="C50">
-        <v>35683899.44635971</v>
+        <v>8884862.566425465</v>
       </c>
       <c r="D50">
-        <v>37237790.00566896</v>
+        <v>38186554.57467408</v>
       </c>
       <c r="E50">
-        <v>8004901</v>
+        <v>39849425.71731169</v>
       </c>
       <c r="F50">
-        <v>20552833.37081907</v>
+        <v>17981359</v>
       </c>
       <c r="G50">
-        <v>9031926.289481398</v>
+        <v>8566316.844403815</v>
       </c>
       <c r="H50">
-        <v>12128009.921795627</v>
+        <v>21994286.08856902</v>
       </c>
       <c r="I50">
-        <v>7940905.153190073</v>
+        <v>9665371.540634686</v>
+      </c>
+      <c r="J50">
+        <v>12978595.947929207</v>
+      </c>
+      <c r="K50">
+        <v>8497832.711932998</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2539,6 +2824,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2546,27 +2833,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -2580,16 +2873,25 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>1071319927</v>
+        <v>1541238882</v>
       </c>
       <c r="C3">
-        <v>1145678606.1181774</v>
+        <v>1146455895</v>
+      </c>
+      <c r="D3">
+        <v>1226029646.320826</v>
       </c>
       <c r="E3">
-        <v>834989957</v>
+        <v>947258013.1185622</v>
       </c>
       <c r="F3">
-        <v>1030914154.2282553</v>
+        <v>1201390769</v>
+      </c>
+      <c r="G3">
+        <v>893551155</v>
+      </c>
+      <c r="H3">
+        <v>1103216302.6750507</v>
       </c>
     </row>
     <row r="4">
@@ -2612,16 +2914,25 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-860906166</v>
+        <v>-1236121917</v>
       </c>
       <c r="C7">
-        <v>-924979120.1603074</v>
+        <v>-921284972</v>
+      </c>
+      <c r="D7">
+        <v>-989851619.3705659</v>
       </c>
       <c r="E7">
-        <v>-672636857</v>
+        <v>-746487967.589632</v>
       </c>
       <c r="F7">
-        <v>-847087512.1092696</v>
+        <v>-928195566</v>
+      </c>
+      <c r="G7">
+        <v>-719811580</v>
+      </c>
+      <c r="H7">
+        <v>-906497160.1354918</v>
       </c>
     </row>
     <row r="8">
@@ -2629,16 +2940,25 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>210413761</v>
+        <v>305116965</v>
       </c>
       <c r="C8">
-        <v>220699485.95786977</v>
+        <v>225170923</v>
+      </c>
+      <c r="D8">
+        <v>236178026.95025992</v>
       </c>
       <c r="E8">
-        <v>162353100</v>
+        <v>200770045.5289297</v>
       </c>
       <c r="F8">
-        <v>183826642.11898565</v>
+        <v>273195203</v>
+      </c>
+      <c r="G8">
+        <v>173739575</v>
+      </c>
+      <c r="H8">
+        <v>196719142.539559</v>
       </c>
     </row>
     <row r="9">
@@ -2666,16 +2986,25 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>210413761</v>
+        <v>305116965</v>
       </c>
       <c r="C13">
-        <v>220699485.95786977</v>
+        <v>225170923</v>
+      </c>
+      <c r="D13">
+        <v>236178026.95025992</v>
       </c>
       <c r="E13">
-        <v>162353100</v>
+        <v>200770045.5289297</v>
       </c>
       <c r="F13">
-        <v>183826642.11898565</v>
+        <v>273195203</v>
+      </c>
+      <c r="G13">
+        <v>173739575</v>
+      </c>
+      <c r="H13">
+        <v>196719142.539559</v>
       </c>
     </row>
     <row r="14"/>
@@ -2684,16 +3013,25 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-21767996</v>
+        <v>-29257767</v>
       </c>
       <c r="C15">
-        <v>-18963632.46903272</v>
+        <v>-23294673</v>
+      </c>
+      <c r="D15">
+        <v>-20293628.14737598</v>
       </c>
       <c r="E15">
-        <v>-17397245</v>
+        <v>-22332830.66915966</v>
       </c>
       <c r="F15">
-        <v>-11588345.345746994</v>
+        <v>-22319685</v>
+      </c>
+      <c r="G15">
+        <v>-18617384</v>
+      </c>
+      <c r="H15">
+        <v>-12401082.528571058</v>
       </c>
     </row>
     <row r="16">
@@ -2701,16 +3039,25 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-75361641</v>
+        <v>-125595919</v>
       </c>
       <c r="C16">
-        <v>-80890184.38665062</v>
+        <v>-80647055</v>
+      </c>
+      <c r="D16">
+        <v>-86563337.76748717</v>
       </c>
       <c r="E16">
-        <v>-78233773</v>
+        <v>-93811149.89127374</v>
       </c>
       <c r="F16">
-        <v>-101415698.67986009</v>
+        <v>-91545530</v>
+      </c>
+      <c r="G16">
+        <v>-83720622</v>
+      </c>
+      <c r="H16">
+        <v>-108528388.78185591</v>
       </c>
     </row>
     <row r="17">
@@ -2718,9 +3065,15 @@
         <v xml:space="preserve">    Araştırma ve Geliştirme Giderleri (-)</v>
       </c>
       <c r="B17">
-        <v>-15857074</v>
-      </c>
-      <c r="E17">
+        <v>-2091542</v>
+      </c>
+      <c r="C17">
+        <v>-16969194</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
         <v>0</v>
       </c>
     </row>
@@ -2729,16 +3082,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>82714125</v>
+        <v>50463955</v>
       </c>
       <c r="C18">
-        <v>65958755.777510285</v>
+        <v>88515199</v>
+      </c>
+      <c r="D18">
+        <v>70584708.12478551</v>
       </c>
       <c r="E18">
-        <v>71315819</v>
+        <v>64810605.1928387</v>
       </c>
       <c r="F18">
-        <v>40442985.98553732</v>
+        <v>87126678</v>
+      </c>
+      <c r="G18">
+        <v>76317484</v>
+      </c>
+      <c r="H18">
+        <v>43279414.9591476</v>
       </c>
     </row>
     <row r="19">
@@ -2746,16 +3108,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-62785176</v>
+        <v>-34677454</v>
       </c>
       <c r="C19">
-        <v>-31810780.29978344</v>
+        <v>-67188552</v>
+      </c>
+      <c r="D19">
+        <v>-34041798.03293808</v>
       </c>
       <c r="E19">
-        <v>-45889031</v>
+        <v>-33970614.0061983</v>
       </c>
       <c r="F19">
-        <v>-22362103.275055707</v>
+        <v>-51037134</v>
+      </c>
+      <c r="G19">
+        <v>-49107413</v>
+      </c>
+      <c r="H19">
+        <v>-23930447.35486515</v>
       </c>
     </row>
     <row r="20">
@@ -2768,16 +3139,25 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>117355999</v>
+        <v>163958238</v>
       </c>
       <c r="C21">
-        <v>142309905.0206809</v>
+        <v>125586648</v>
+      </c>
+      <c r="D21">
+        <v>152290669.99131727</v>
       </c>
       <c r="E21">
-        <v>92148870</v>
+        <v>115466056.1551367</v>
       </c>
       <c r="F21">
-        <v>88903480.80386013</v>
+        <v>195419532</v>
+      </c>
+      <c r="G21">
+        <v>98611640</v>
+      </c>
+      <c r="H21">
+        <v>95138638.8334145</v>
       </c>
     </row>
     <row r="22"/>
@@ -2796,16 +3176,25 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>13858660</v>
+        <v>34526535</v>
       </c>
       <c r="C25">
-        <v>5537405.145540388</v>
+        <v>14830623</v>
+      </c>
+      <c r="D25">
+        <v>5925765.599416029</v>
       </c>
       <c r="E25">
-        <v>6788928</v>
+        <v>3034670.3642650433</v>
       </c>
       <c r="F25">
-        <v>12441872.29655622</v>
+        <v>3763900</v>
+      </c>
+      <c r="G25">
+        <v>7265063</v>
+      </c>
+      <c r="H25">
+        <v>13314470.751094952</v>
       </c>
     </row>
     <row r="26">
@@ -2816,9 +3205,18 @@
         <v>0</v>
       </c>
       <c r="C26">
-        <v>-38318.89633936377</v>
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>-41006.35437850584</v>
       </c>
       <c r="E26">
+        <v>-553.5529288221151</v>
+      </c>
+      <c r="F26">
+        <v>-635967</v>
+      </c>
+      <c r="G26">
         <v>0</v>
       </c>
     </row>
@@ -2857,16 +3255,25 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>131214659</v>
+        <v>198484773</v>
       </c>
       <c r="C33">
-        <v>147808991.2698819</v>
+        <v>140417271</v>
+      </c>
+      <c r="D33">
+        <v>158175429.23635477</v>
       </c>
       <c r="E33">
-        <v>98937798</v>
+        <v>118500172.96647292</v>
       </c>
       <c r="F33">
-        <v>101345353.10041636</v>
+        <v>198547465</v>
+      </c>
+      <c r="G33">
+        <v>105876703</v>
+      </c>
+      <c r="H33">
+        <v>108453109.58450937</v>
       </c>
     </row>
     <row r="34"/>
@@ -2880,16 +3287,25 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-11158657</v>
+        <v>-24176517</v>
       </c>
       <c r="C36">
-        <v>-14088585.655934907</v>
+        <v>-11941258</v>
+      </c>
+      <c r="D36">
+        <v>-15076674.729426533</v>
       </c>
       <c r="E36">
-        <v>-5431348</v>
+        <v>-17110003.45957022</v>
       </c>
       <c r="F36">
-        <v>-5924232.1042041965</v>
+        <v>-11402093</v>
+      </c>
+      <c r="G36">
+        <v>-5812270</v>
+      </c>
+      <c r="H36">
+        <v>-6339722.285685014</v>
       </c>
     </row>
     <row r="37">
@@ -2897,16 +3313,25 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>-96239172</v>
+        <v>-123787272</v>
       </c>
       <c r="C37">
-        <v>-47852238.73556507</v>
+        <v>-102988812</v>
+      </c>
+      <c r="D37">
+        <v>-51208308.350459754</v>
       </c>
       <c r="E37">
-        <v>-88692832</v>
+        <v>-81315028.71585178</v>
       </c>
       <c r="F37">
-        <v>-78067113.26206148</v>
+        <v>-79676924</v>
+      </c>
+      <c r="G37">
+        <v>-94913216</v>
+      </c>
+      <c r="H37">
+        <v>-83542273.33114773</v>
       </c>
     </row>
     <row r="38">
@@ -2914,16 +3339,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>23816830</v>
+        <v>50520984</v>
       </c>
       <c r="C38">
-        <v>85868166.87838195</v>
+        <v>25487201</v>
+      </c>
+      <c r="D38">
+        <v>91890446.15646851</v>
       </c>
       <c r="E38">
-        <v>4813618</v>
+        <v>20075140.79105091</v>
       </c>
       <c r="F38">
-        <v>17354007.734150678</v>
+        <v>107468448</v>
+      </c>
+      <c r="G38">
+        <v>5151217</v>
+      </c>
+      <c r="H38">
+        <v>18571113.9676767</v>
       </c>
     </row>
     <row r="39"/>
@@ -2932,16 +3366,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>-28709366</v>
+        <v>-35262702</v>
       </c>
       <c r="C40">
-        <v>-29958676.467569947</v>
+        <v>-30722869</v>
+      </c>
+      <c r="D40">
+        <v>-32059798.72333069</v>
       </c>
       <c r="E40">
-        <v>-28694480</v>
+        <v>-21480298.516635507</v>
       </c>
       <c r="F40">
-        <v>-12695901.423638314</v>
+        <v>-42937382</v>
+      </c>
+      <c r="G40">
+        <v>-30706939</v>
+      </c>
+      <c r="H40">
+        <v>-13586315.960709974</v>
       </c>
     </row>
     <row r="41">
@@ -2949,16 +3392,25 @@
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
       <c r="B41">
-        <v>-29808570</v>
+        <v>-32671544</v>
       </c>
       <c r="C41">
-        <v>-36109149.84145686</v>
+        <v>-31899165</v>
+      </c>
+      <c r="D41">
+        <v>-38641629.487232044</v>
       </c>
       <c r="E41">
-        <v>-30661686</v>
+        <v>-19483515.384704053</v>
       </c>
       <c r="F41">
-        <v>-11854154.490786508</v>
+        <v>-42136252</v>
+      </c>
+      <c r="G41">
+        <v>-32812113</v>
+      </c>
+      <c r="H41">
+        <v>-12685533.936096087</v>
       </c>
     </row>
     <row r="42">
@@ -2966,16 +3418,25 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>1099204</v>
+        <v>-2591158</v>
       </c>
       <c r="C42">
-        <v>6150473.373886911</v>
+        <v>1176296</v>
+      </c>
+      <c r="D42">
+        <v>6581830.763901341</v>
       </c>
       <c r="E42">
-        <v>1967206</v>
+        <v>-1996783.1319314605</v>
       </c>
       <c r="F42">
-        <v>-841746.9328518133</v>
+        <v>-801130</v>
+      </c>
+      <c r="G42">
+        <v>2105174</v>
+      </c>
+      <c r="H42">
+        <v>-900782.0246138871</v>
       </c>
     </row>
     <row r="43">
@@ -2983,16 +3444,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>-4892536</v>
+        <v>15258282</v>
       </c>
       <c r="C43">
-        <v>55909490.41081202</v>
+        <v>-5235668</v>
+      </c>
+      <c r="D43">
+        <v>59830647.43313785</v>
       </c>
       <c r="E43">
-        <v>-23880862</v>
+        <v>-1405157.7255846113</v>
       </c>
       <c r="F43">
-        <v>4658106.310512349</v>
+        <v>64531066</v>
+      </c>
+      <c r="G43">
+        <v>-25555722</v>
+      </c>
+      <c r="H43">
+        <v>4984798.00696668</v>
       </c>
     </row>
     <row r="44">
@@ -3006,16 +3476,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>-4892536</v>
+        <v>15258282</v>
       </c>
       <c r="C46">
-        <v>55909490.41081202</v>
+        <v>-5235668</v>
+      </c>
+      <c r="D46">
+        <v>59830647.43313785</v>
       </c>
       <c r="E46">
-        <v>-23880862</v>
+        <v>-1405157.7255846113</v>
       </c>
       <c r="F46">
-        <v>4658106.310512349</v>
+        <v>64531066</v>
+      </c>
+      <c r="G46">
+        <v>-25555722</v>
+      </c>
+      <c r="H46">
+        <v>4984798.00696668</v>
       </c>
     </row>
     <row r="47">
@@ -3025,7 +3504,13 @@
       <c r="B47">
         <v>0</v>
       </c>
-      <c r="E47">
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
         <v>0</v>
       </c>
     </row>
@@ -3034,16 +3519,25 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>-4892536</v>
+        <v>15258282</v>
       </c>
       <c r="C48">
-        <v>55909490.41081202</v>
+        <v>-5235668</v>
+      </c>
+      <c r="D48">
+        <v>59830647.43313785</v>
       </c>
       <c r="E48">
-        <v>-23880862</v>
+        <v>-1405157.7255846113</v>
       </c>
       <c r="F48">
-        <v>4658106.310512349</v>
+        <v>64531066</v>
+      </c>
+      <c r="G48">
+        <v>-25555722</v>
+      </c>
+      <c r="H48">
+        <v>4984798.00696668</v>
       </c>
     </row>
     <row r="49"/>
@@ -3052,28 +3546,37 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>8302570</v>
+        <v>8017573.433574535</v>
       </c>
       <c r="C50">
-        <v>-1553890.5593092516</v>
+        <v>8884862.566425465</v>
+      </c>
+      <c r="D50">
+        <v>-1662871.1426376104</v>
       </c>
       <c r="E50">
-        <v>8004901</v>
+        <v>21868066.717311688</v>
       </c>
       <c r="F50">
-        <v>11520907.081337672</v>
+        <v>9415042.155596185</v>
+      </c>
+      <c r="G50">
+        <v>8566316.844403815</v>
+      </c>
+      <c r="H50">
+        <v>12328914.547934333</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -3084,6 +3587,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3091,27 +3596,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -3125,22 +3636,25 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>4224830031.4965496</v>
+        <v>4860982436.439388</v>
       </c>
       <c r="C3">
-        <v>3988500061.4965496</v>
+        <v>4521134323.439388</v>
       </c>
       <c r="D3">
-        <v>3873735609.6066275</v>
-      </c>
-      <c r="F3">
-        <v>3879530777.6112375</v>
+        <v>4268229583.4393883</v>
+      </c>
+      <c r="E3">
+        <v>4145416239.793613</v>
       </c>
       <c r="H3">
-        <v>5604942822.076969</v>
-      </c>
-      <c r="I3">
-        <v>4857887189.415232</v>
+        <v>4151617846.1962457</v>
+      </c>
+      <c r="J3">
+        <v>5998039964.351613</v>
+      </c>
+      <c r="K3">
+        <v>5198590320.967268</v>
       </c>
     </row>
     <row r="4">
@@ -3163,22 +3677,25 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-3350814080.469434</v>
+        <v>-3893746475.960198</v>
       </c>
       <c r="C7">
-        <v>-3162544771.469434</v>
+        <v>-3585820124.960198</v>
       </c>
       <c r="D7">
-        <v>-3084653163.418396</v>
-      </c>
-      <c r="F7">
-        <v>-3089128155.099466</v>
+        <v>-3384346732.960198</v>
+      </c>
+      <c r="E7">
+        <v>-3300992273.725124</v>
       </c>
       <c r="H7">
-        <v>-4460743739.996516</v>
-      </c>
-      <c r="I7">
-        <v>-3916734455.634033</v>
+        <v>-3305781114.538535</v>
+      </c>
+      <c r="J7">
+        <v>-4773593607.029122</v>
+      </c>
+      <c r="K7">
+        <v>-4191430767.5203757</v>
       </c>
     </row>
     <row r="8">
@@ -3186,22 +3703,25 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>874015951.0271153</v>
+        <v>967235960.4791896</v>
       </c>
       <c r="C8">
-        <v>825955290.0271153</v>
+        <v>935314198.4791896</v>
       </c>
       <c r="D8">
-        <v>789082446.1882312</v>
-      </c>
-      <c r="F8">
-        <v>790402622.5117719</v>
+        <v>883882850.4791896</v>
+      </c>
+      <c r="E8">
+        <v>844423966.0684887</v>
       </c>
       <c r="H8">
-        <v>1144199082.0804527</v>
-      </c>
-      <c r="I8">
-        <v>941152733.7811985</v>
+        <v>845836731.6577108</v>
+      </c>
+      <c r="J8">
+        <v>1224446357.322491</v>
+      </c>
+      <c r="K8">
+        <v>1007159553.446892</v>
       </c>
     </row>
     <row r="9">
@@ -3229,22 +3749,25 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>874015951.0271153</v>
+        <v>967235960.4791896</v>
       </c>
       <c r="C13">
-        <v>825955290.0271153</v>
+        <v>935314198.4791896</v>
       </c>
       <c r="D13">
-        <v>789082446.1882312</v>
-      </c>
-      <c r="F13">
-        <v>790402622.5117719</v>
+        <v>883882850.4791896</v>
+      </c>
+      <c r="E13">
+        <v>844423966.0684887</v>
       </c>
       <c r="H13">
-        <v>1144199082.0804527</v>
-      </c>
-      <c r="I13">
-        <v>941152733.7811985</v>
+        <v>845836731.6577108</v>
+      </c>
+      <c r="J13">
+        <v>1224446357.322491</v>
+      </c>
+      <c r="K13">
+        <v>1007159553.446892</v>
       </c>
     </row>
     <row r="14"/>
@@ -3253,22 +3776,25 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-82457725.77949384</v>
+        <v>-95178898.81653564</v>
       </c>
       <c r="C15">
-        <v>-78086974.77949384</v>
+        <v>-88240816.81653564</v>
       </c>
       <c r="D15">
-        <v>-70711687.65620811</v>
-      </c>
-      <c r="F15">
-        <v>-41298333.03440366</v>
+        <v>-83563527.81653564</v>
+      </c>
+      <c r="E15">
+        <v>-75670982.19773072</v>
       </c>
       <c r="H15">
-        <v>-38548393.7578681</v>
-      </c>
-      <c r="I15">
-        <v>-38813532.745884165</v>
+        <v>-44194750.93051251</v>
+      </c>
+      <c r="J15">
+        <v>-41251947.37233307</v>
+      </c>
+      <c r="K15">
+        <v>-41535681.62203212</v>
       </c>
     </row>
     <row r="16">
@@ -3276,22 +3802,25 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-329460673.7734464</v>
+        <v>-386617461.6587609</v>
       </c>
       <c r="C16">
-        <v>-332332805.7734464</v>
+        <v>-352567072.6587609</v>
       </c>
       <c r="D16">
-        <v>-352858320.0666559</v>
-      </c>
-      <c r="F16">
-        <v>-299490895.9074183</v>
+        <v>-355640639.6587609</v>
+      </c>
+      <c r="E16">
+        <v>-377605690.6731297</v>
       </c>
       <c r="H16">
-        <v>-293127392.93088245</v>
-      </c>
-      <c r="I16">
-        <v>-226074440.19906828</v>
+        <v>-320495394.8034219</v>
+      </c>
+      <c r="J16">
+        <v>-313685593.81558794</v>
+      </c>
+      <c r="K16">
+        <v>-241929948.311221</v>
       </c>
     </row>
     <row r="17">
@@ -3299,19 +3828,22 @@
         <v xml:space="preserve">    Araştırma ve Geliştirme Giderleri (-)</v>
       </c>
       <c r="B17">
-        <v>-28540813.559232414</v>
+        <v>-32634037.13592706</v>
       </c>
       <c r="C17">
-        <v>-12683739.559232414</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
+        <v>-30542495.13592706</v>
+      </c>
+      <c r="D17">
+        <v>-13573301.135927057</v>
       </c>
       <c r="H17">
-        <v>-56053.29796492187</v>
-      </c>
-      <c r="I17">
-        <v>-3111197.9290582747</v>
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>-59984.54078836156</v>
+      </c>
+      <c r="K17">
+        <v>-3329398.7303485903</v>
       </c>
     </row>
     <row r="18">
@@ -3319,22 +3851,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>290652559.4044003</v>
+        <v>274374467.3176242</v>
       </c>
       <c r="C18">
-        <v>279254253.4044003</v>
+        <v>311037190.3176242</v>
       </c>
       <c r="D18">
-        <v>253738483.61242732</v>
-      </c>
-      <c r="F18">
-        <v>217764157.4795311</v>
+        <v>298839475.3176242</v>
+      </c>
+      <c r="E18">
+        <v>271534182.1519863</v>
       </c>
       <c r="H18">
-        <v>647647501.0384675</v>
-      </c>
-      <c r="I18">
-        <v>384154777.40959114</v>
+        <v>233036832.10127297</v>
+      </c>
+      <c r="J18">
+        <v>693069620.3965372</v>
+      </c>
+      <c r="K18">
+        <v>411097094.2154036</v>
       </c>
     </row>
     <row r="19">
@@ -3342,22 +3877,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-174032500.56787816</v>
+        <v>-169878418.03913638</v>
       </c>
       <c r="C19">
-        <v>-157136355.56787816</v>
+        <v>-186238098.03913638</v>
       </c>
       <c r="D19">
-        <v>-147687678.54315042</v>
-      </c>
-      <c r="F19">
-        <v>-97325614.82141343</v>
+        <v>-168156959.03913638</v>
+      </c>
+      <c r="E19">
+        <v>-158045608.36106345</v>
       </c>
       <c r="H19">
-        <v>-376311140.7615194</v>
-      </c>
-      <c r="I19">
-        <v>-226259537.7890303</v>
+        <v>-104151450.92195785</v>
+      </c>
+      <c r="J19">
+        <v>-402703351.83935666</v>
+      </c>
+      <c r="K19">
+        <v>-242128027.5382783</v>
       </c>
     </row>
     <row r="20">
@@ -3370,22 +3908,25 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>550176796.7514648</v>
+        <v>557301612.146454</v>
       </c>
       <c r="C21">
-        <v>524969667.7514649</v>
+        <v>588762906.146454</v>
       </c>
       <c r="D21">
-        <v>471563243.5346441</v>
-      </c>
-      <c r="F21">
-        <v>570051936.2280676</v>
+        <v>561787898.146454</v>
+      </c>
+      <c r="E21">
+        <v>504635866.9885512</v>
       </c>
       <c r="H21">
-        <v>1083803602.3706853</v>
-      </c>
-      <c r="I21">
-        <v>831048802.5277486</v>
+        <v>610031967.1030916</v>
+      </c>
+      <c r="J21">
+        <v>1159815100.1509619</v>
+      </c>
+      <c r="K21">
+        <v>889333591.4604155</v>
       </c>
     </row>
     <row r="22"/>
@@ -3404,22 +3945,25 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>25749073.73580127</v>
+        <v>58317593.96368107</v>
       </c>
       <c r="C25">
-        <v>18679341.73580127</v>
+        <v>27554958.963681072</v>
       </c>
       <c r="D25">
-        <v>25583808.886817098</v>
-      </c>
-      <c r="F25">
-        <v>47163965.46403822</v>
+        <v>19989398.963681072</v>
+      </c>
+      <c r="E25">
+        <v>27378104.115359996</v>
       </c>
       <c r="H25">
-        <v>17634597.748055562</v>
-      </c>
-      <c r="I25">
-        <v>4500572.091853142</v>
+        <v>50471763.71119023</v>
+      </c>
+      <c r="J25">
+        <v>18871382.885741364</v>
+      </c>
+      <c r="K25">
+        <v>4816215.281100325</v>
       </c>
     </row>
     <row r="26">
@@ -3427,12 +3971,15 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
       <c r="B26">
-        <v>-633123.4200582264</v>
+        <v>-41559.90730732796</v>
       </c>
       <c r="C26">
-        <v>-633123.4200582264</v>
-      </c>
-      <c r="F26">
+        <v>-677526.907307328</v>
+      </c>
+      <c r="D26">
+        <v>-677526.907307328</v>
+      </c>
+      <c r="H26">
         <v>0</v>
       </c>
     </row>
@@ -3471,22 +4018,25 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>575292747.0672079</v>
+        <v>615577646.2028277</v>
       </c>
       <c r="C33">
-        <v>543015886.0672079</v>
+        <v>615640338.2028277</v>
       </c>
       <c r="D33">
-        <v>496552247.8977424</v>
-      </c>
-      <c r="F33">
-        <v>617215901.6921059</v>
+        <v>581099770.2028277</v>
+      </c>
+      <c r="E33">
+        <v>531377450.5509823</v>
       </c>
       <c r="H33">
-        <v>1101438200.1187408</v>
-      </c>
-      <c r="I33">
-        <v>835549374.6196017</v>
+        <v>660503730.8142818</v>
+      </c>
+      <c r="J33">
+        <v>1178686483.036703</v>
+      </c>
+      <c r="K33">
+        <v>894149806.7415159</v>
       </c>
     </row>
     <row r="34"/>
@@ -3500,22 +4050,25 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-51890724.52591302</v>
+        <v>-68304453.18899676</v>
       </c>
       <c r="C36">
-        <v>-46163415.52591302</v>
+        <v>-55530029.188996755</v>
       </c>
       <c r="D36">
-        <v>-37999061.97418231</v>
-      </c>
-      <c r="F36">
-        <v>-29640590.673012946</v>
+        <v>-49401041.188996755</v>
+      </c>
+      <c r="E36">
+        <v>-40664088.74525523</v>
       </c>
       <c r="H36">
-        <v>-39465468.98116891</v>
-      </c>
-      <c r="I36">
-        <v>-13596845.560228465</v>
+        <v>-31719404.29498246</v>
+      </c>
+      <c r="J36">
+        <v>-42233340.76282561</v>
+      </c>
+      <c r="K36">
+        <v>-14550446.92661937</v>
       </c>
     </row>
     <row r="37">
@@ -3523,22 +4076,25 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>-294532336.9384183</v>
+        <v>-359299421.06631154</v>
       </c>
       <c r="C37">
-        <v>-286985996.9384183</v>
+        <v>-315189073.06631154</v>
       </c>
       <c r="D37">
-        <v>-317200871.46491474</v>
-      </c>
-      <c r="F37">
-        <v>-410586857.63154584</v>
+        <v>-307113477.06631154</v>
+      </c>
+      <c r="E37">
+        <v>-339447442.0469995</v>
       </c>
       <c r="H37">
-        <v>-509696226.8713128</v>
-      </c>
-      <c r="I37">
-        <v>-396942536.5631682</v>
+        <v>-439382962.3401891</v>
+      </c>
+      <c r="J37">
+        <v>-545443269.5390979</v>
+      </c>
+      <c r="K37">
+        <v>-424781710.2574341</v>
       </c>
     </row>
     <row r="38">
@@ -3546,22 +4102,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>228869685.6028766</v>
+        <v>187973771.94751942</v>
       </c>
       <c r="C38">
-        <v>209866473.6028766</v>
+        <v>244921235.94751942</v>
       </c>
       <c r="D38">
-        <v>141352314.45864534</v>
-      </c>
-      <c r="F38">
-        <v>176988453.38754708</v>
+        <v>224585251.94751942</v>
+      </c>
+      <c r="E38">
+        <v>151265919.7587276</v>
       </c>
       <c r="H38">
-        <v>552276504.2662592</v>
-      </c>
-      <c r="I38">
-        <v>425009992.49620503</v>
+        <v>189401364.17911026</v>
+      </c>
+      <c r="J38">
+        <v>591009872.7347797</v>
+      </c>
+      <c r="K38">
+        <v>454817649.55746233</v>
       </c>
     </row>
     <row r="39"/>
@@ -3570,22 +4129,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>-118863942.74702251</v>
+        <v>-119525668.2399662</v>
       </c>
       <c r="C40">
-        <v>-118849056.74702251</v>
+        <v>-127200348.2399662</v>
       </c>
       <c r="D40">
-        <v>-101586281.70309088</v>
-      </c>
-      <c r="F40">
-        <v>-79768355.83487721</v>
+        <v>-127184418.2399662</v>
+      </c>
+      <c r="E40">
+        <v>-108710935.47734548</v>
       </c>
       <c r="H40">
-        <v>-216247912.35827166</v>
-      </c>
-      <c r="I40">
-        <v>-164405674.24938315</v>
+        <v>-85362830.87557308</v>
+      </c>
+      <c r="J40">
+        <v>-231414246.62239075</v>
+      </c>
+      <c r="K40">
+        <v>-175936104.223907</v>
       </c>
     </row>
     <row r="41">
@@ -3593,22 +4155,25 @@
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
       <c r="B41">
-        <v>-123499075.4489153</v>
+        <v>-122695853.8719361</v>
       </c>
       <c r="C41">
-        <v>-124352191.4489153</v>
+        <v>-132160561.8719361</v>
       </c>
       <c r="D41">
-        <v>-100097196.09824495</v>
-      </c>
-      <c r="F41">
-        <v>-83822704.58793865</v>
+        <v>-133073509.8719361</v>
+      </c>
+      <c r="E41">
+        <v>-107117414.32080014</v>
       </c>
       <c r="H41">
-        <v>-219257109.96743193</v>
-      </c>
-      <c r="I41">
-        <v>-180233329.48582047</v>
+        <v>-89701527.38367954</v>
+      </c>
+      <c r="J41">
+        <v>-234634491.34090623</v>
+      </c>
+      <c r="K41">
+        <v>-192873816.46535873</v>
       </c>
     </row>
     <row r="42">
@@ -3616,22 +4181,25 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>4635132.701892785</v>
+        <v>3170185.6319698803</v>
       </c>
       <c r="C42">
-        <v>5503134.701892785</v>
+        <v>4960213.63196988</v>
       </c>
       <c r="D42">
-        <v>-1489085.6048459394</v>
-      </c>
-      <c r="F42">
-        <v>4054348.7530614394</v>
+        <v>5889091.63196988</v>
+      </c>
+      <c r="E42">
+        <v>-1593521.1565453475</v>
       </c>
       <c r="H42">
-        <v>3009197.6091602705</v>
-      </c>
-      <c r="I42">
-        <v>15827655.236437319</v>
+        <v>4338696.508106448</v>
+      </c>
+      <c r="J42">
+        <v>3220244.718515483</v>
+      </c>
+      <c r="K42">
+        <v>16937712.241451737</v>
       </c>
     </row>
     <row r="43">
@@ -3639,22 +4207,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>110005742.8558541</v>
+        <v>68448103.70755324</v>
       </c>
       <c r="C43">
-        <v>91017416.8558541</v>
+        <v>117720887.70755324</v>
       </c>
       <c r="D43">
-        <v>39766032.75555442</v>
-      </c>
-      <c r="F43">
-        <v>97220097.55266985</v>
+        <v>97400833.70755324</v>
+      </c>
+      <c r="E43">
+        <v>42554984.28138207</v>
       </c>
       <c r="H43">
-        <v>336028591.9079875</v>
-      </c>
-      <c r="I43">
-        <v>260604318.24682188</v>
+        <v>104038533.30353715</v>
+      </c>
+      <c r="J43">
+        <v>359595626.1123889</v>
+      </c>
+      <c r="K43">
+        <v>278881545.33355534</v>
       </c>
     </row>
     <row r="44">
@@ -3668,22 +4239,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>110005742.8558541</v>
+        <v>68448103.70755324</v>
       </c>
       <c r="C46">
-        <v>91017416.8558541</v>
+        <v>117720887.70755324</v>
       </c>
       <c r="D46">
-        <v>39766032.75555442</v>
-      </c>
-      <c r="F46">
-        <v>97220097.55266985</v>
+        <v>97400833.70755324</v>
+      </c>
+      <c r="E46">
+        <v>42554984.28138207</v>
       </c>
       <c r="H46">
-        <v>336028591.9079875</v>
-      </c>
-      <c r="I46">
-        <v>260604318.24682188</v>
+        <v>104038533.30353715</v>
+      </c>
+      <c r="J46">
+        <v>359595626.1123889</v>
+      </c>
+      <c r="K46">
+        <v>278881545.33355534</v>
       </c>
     </row>
     <row r="47">
@@ -3696,7 +4270,10 @@
       <c r="C47">
         <v>0</v>
       </c>
-      <c r="F47">
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="H47">
         <v>0</v>
       </c>
     </row>
@@ -3705,22 +4282,25 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>110005742.8558541</v>
+        <v>68448103.70755324</v>
       </c>
       <c r="C48">
-        <v>91017416.8558541</v>
+        <v>117720887.70755324</v>
       </c>
       <c r="D48">
-        <v>39766032.75555442</v>
-      </c>
-      <c r="F48">
-        <v>97220097.55266985</v>
+        <v>97400833.70755324</v>
+      </c>
+      <c r="E48">
+        <v>42554984.28138207</v>
       </c>
       <c r="H48">
-        <v>336028591.9079875</v>
-      </c>
-      <c r="I48">
-        <v>260604318.24682188</v>
+        <v>104038533.30353715</v>
+      </c>
+      <c r="J48">
+        <v>359595626.1123889</v>
+      </c>
+      <c r="K48">
+        <v>278881545.33355534</v>
       </c>
     </row>
     <row r="49"/>
@@ -3729,34 +4309,37 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>35981568.44635971</v>
+        <v>37107631.57467408</v>
       </c>
       <c r="C50">
-        <v>35683899.44635971</v>
+        <v>38505100.296695724</v>
       </c>
       <c r="D50">
-        <v>48758697.08700663</v>
-      </c>
-      <c r="F50">
-        <v>20552833.37081907</v>
+        <v>38186554.57467408</v>
+      </c>
+      <c r="E50">
+        <v>52178340.26524602</v>
       </c>
       <c r="H50">
-        <v>12128009.921795627</v>
-      </c>
-      <c r="I50">
-        <v>7940905.153190073</v>
+        <v>21994286.08856902</v>
+      </c>
+      <c r="J50">
+        <v>12978595.947929207</v>
+      </c>
+      <c r="K50">
+        <v>8497832.711932998</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -3767,6 +4350,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3774,27 +4359,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -3808,28 +4399,34 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>-109268235</v>
+        <v>-91725350</v>
       </c>
       <c r="C3">
-        <v>-96275191.55551001</v>
+        <v>-116931654.9997026</v>
       </c>
       <c r="D3">
-        <v>-100467590.45455866</v>
+        <v>-103027357.25528264</v>
       </c>
       <c r="E3">
-        <v>-82600959</v>
+        <v>-107513785.92034426</v>
       </c>
       <c r="F3">
-        <v>39657659.89161238</v>
+        <v>-216771035</v>
       </c>
       <c r="G3">
-        <v>61891024.791998565</v>
+        <v>-88394095.87271708</v>
       </c>
       <c r="H3">
-        <v>664130208.905412</v>
+        <v>42439010.793407276</v>
       </c>
       <c r="I3">
-        <v>307421796.0234044</v>
+        <v>66231690.83454141</v>
+      </c>
+      <c r="J3">
+        <v>710708326.7393131</v>
+      </c>
+      <c r="K3">
+        <v>328982520.7847246</v>
       </c>
     </row>
     <row r="4">
@@ -3837,28 +4434,34 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>-4892536</v>
+        <v>10022614</v>
       </c>
       <c r="C4">
-        <v>91017416.8558541</v>
+        <v>-5235669.191742916</v>
       </c>
       <c r="D4">
-        <v>94980860.84446493</v>
+        <v>97400833.70755324</v>
       </c>
       <c r="E4">
-        <v>-23880863</v>
+        <v>101642249.93512282</v>
       </c>
       <c r="F4">
-        <v>97220097.55266985</v>
+        <v>38975344</v>
       </c>
       <c r="G4">
-        <v>92561991.2421575</v>
+        <v>-25555723.79668403</v>
       </c>
       <c r="H4">
-        <v>336028591.9079875</v>
+        <v>104038533.30353715</v>
       </c>
       <c r="I4">
-        <v>260604318.24682188</v>
+        <v>99053735.29657046</v>
+      </c>
+      <c r="J4">
+        <v>359595626.1123889</v>
+      </c>
+      <c r="K4">
+        <v>278881545.33355534</v>
       </c>
     </row>
     <row r="5">
@@ -3866,28 +4469,34 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>53565643</v>
+        <v>136518846</v>
       </c>
       <c r="C5">
-        <v>170485986.91472936</v>
+        <v>57322416.59356203</v>
       </c>
       <c r="D5">
-        <v>177909969.91420856</v>
+        <v>182442853.62710348</v>
       </c>
       <c r="E5">
-        <v>60240408</v>
+        <v>190387510.35939866</v>
       </c>
       <c r="F5">
-        <v>156963185.4524271</v>
+        <v>120920991</v>
       </c>
       <c r="G5">
-        <v>273165820.7248077</v>
+        <v>64465309.66018921</v>
       </c>
       <c r="H5">
-        <v>409510620.665386</v>
+        <v>167971643.8082627</v>
       </c>
       <c r="I5">
-        <v>214635860.09236538</v>
+        <v>292324036.4109828</v>
+      </c>
+      <c r="J5">
+        <v>438231244.55482423</v>
+      </c>
+      <c r="K5">
+        <v>229689134.6591707</v>
       </c>
     </row>
     <row r="6">
@@ -3895,28 +4504,34 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>8302570</v>
+        <v>16902436</v>
       </c>
       <c r="C6">
-        <v>35683899.44635971</v>
+        <v>8884862.566425465</v>
       </c>
       <c r="D6">
-        <v>37237790.00566896</v>
+        <v>38186554.57467408</v>
       </c>
       <c r="E6">
-        <v>8004901</v>
+        <v>39849425.71731169</v>
       </c>
       <c r="F6">
-        <v>20552833.37081907</v>
+        <v>17981359</v>
       </c>
       <c r="G6">
-        <v>9031926.289481398</v>
+        <v>8566316.844403815</v>
       </c>
       <c r="H6">
-        <v>12128009.921795627</v>
+        <v>21994286.08856902</v>
       </c>
       <c r="I6">
-        <v>7940905.153190073</v>
+        <v>9665371.540634686</v>
+      </c>
+      <c r="J6">
+        <v>12978595.947929207</v>
+      </c>
+      <c r="K6">
+        <v>8497832.711932998</v>
       </c>
     </row>
     <row r="7">
@@ -3924,28 +4539,34 @@
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B7">
-        <v>-166258</v>
+        <v>2002668</v>
       </c>
       <c r="C7">
-        <v>12034833.886250772</v>
+        <v>-177918.34101594627</v>
       </c>
       <c r="D7">
-        <v>12558903.281123092</v>
+        <v>12878885.102937788</v>
       </c>
       <c r="E7">
-        <v>7066461</v>
+        <v>13439709.588453759</v>
       </c>
       <c r="F7">
-        <v>2528499.148221192</v>
+        <v>9604458</v>
       </c>
       <c r="G7">
-        <v>8917055.433382567</v>
+        <v>7562060.279649008</v>
       </c>
       <c r="H7">
-        <v>4570102.25856392</v>
+        <v>2705832.94465077</v>
       </c>
       <c r="I7">
-        <v>1411603.7884611553</v>
+        <v>9542444.33022565</v>
+      </c>
+      <c r="J7">
+        <v>4890621.877545272</v>
+      </c>
+      <c r="K7">
+        <v>1510605.2293112723</v>
       </c>
     </row>
     <row r="8">
@@ -3953,28 +4574,34 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>7084232</v>
+        <v>29853483</v>
       </c>
       <c r="C8">
-        <v>5478961.730900688</v>
+        <v>7581077.631224236</v>
       </c>
       <c r="D8">
-        <v>5717548.635470293</v>
+        <v>5863223.313474888</v>
       </c>
       <c r="E8">
-        <v>4665848</v>
+        <v>6118543.275516739</v>
       </c>
       <c r="F8">
-        <v>5881677.683425967</v>
+        <v>6693213</v>
       </c>
       <c r="G8">
-        <v>4477766.945458995</v>
+        <v>4993082.652218666</v>
       </c>
       <c r="H8">
-        <v>4191467.942001269</v>
+        <v>6294183.352534386</v>
       </c>
       <c r="I8">
-        <v>7880200.371254486</v>
+        <v>4791810.718233743</v>
+      </c>
+      <c r="J8">
+        <v>4485432.416258997</v>
+      </c>
+      <c r="K8">
+        <v>8432870.459928798</v>
       </c>
     </row>
     <row r="9">
@@ -3997,28 +4624,34 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>2765259</v>
+        <v>2956424</v>
       </c>
       <c r="C12">
-        <v>5825443.91624619</v>
+        <v>2959197.7153545367</v>
       </c>
       <c r="D12">
-        <v>6079118.707430839</v>
+        <v>6234005.685500602</v>
       </c>
       <c r="E12">
-        <v>1475117</v>
+        <v>6505471.7082191445</v>
       </c>
       <c r="F12">
-        <v>2490677.642644719</v>
+        <v>3152505</v>
       </c>
       <c r="G12">
-        <v>114668.37844314103</v>
+        <v>1578572.877361809</v>
       </c>
       <c r="H12">
-        <v>901301.7737537245</v>
+        <v>2665358.865046231</v>
       </c>
       <c r="I12">
-        <v>774900.6955009719</v>
+        <v>122710.5321824655</v>
+      </c>
+      <c r="J12">
+        <v>964513.6856030532</v>
+      </c>
+      <c r="K12">
+        <v>829247.5922700614</v>
       </c>
     </row>
     <row r="13">
@@ -4061,59 +4694,71 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>28709366</v>
+        <v>65985571</v>
       </c>
       <c r="C20">
-        <v>118849056.74702251</v>
+        <v>30722869.09706368</v>
       </c>
       <c r="D20">
-        <v>124024458.2543179</v>
+        <v>127184418.2399662</v>
       </c>
       <c r="E20">
-        <v>28694480</v>
+        <v>132722791.4326512</v>
       </c>
       <c r="F20">
-        <v>79768354.73445517</v>
+        <v>73644321</v>
       </c>
       <c r="G20">
-        <v>67072456.61208297</v>
+        <v>30706939.08212086</v>
       </c>
       <c r="H20">
-        <v>216247912.35827166</v>
+        <v>85362829.69797404</v>
       </c>
       <c r="I20">
-        <v>164405673.14896113</v>
+        <v>71776517.27006122</v>
+      </c>
+      <c r="J20">
+        <v>231414246.62239075</v>
+      </c>
+      <c r="K20">
+        <v>175936103.04630795</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="D21">
-        <v>-30220235.78268405</v>
-      </c>
-      <c r="G21">
-        <v>183551947.06595862</v>
-      </c>
-      <c r="H21">
-        <v>226614774.93214035</v>
+      <c r="E21">
+        <v>-32339702.24329586</v>
       </c>
       <c r="I21">
-        <v>32222575.834575552</v>
+        <v>196425182.01964504</v>
+      </c>
+      <c r="J21">
+        <v>242508178.8884051</v>
+      </c>
+      <c r="K21">
+        <v>34482474.44182056</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C22">
-        <v>633123.4200582264</v>
+      <c r="B22">
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>660693.3938933427</v>
+        <v>677526.907307328</v>
+      </c>
+      <c r="E22">
+        <v>707030.4740926672</v>
       </c>
       <c r="F22">
-        <v>-696175.4022089605</v>
+        <v>635967</v>
+      </c>
+      <c r="H22">
+        <v>-745000.9781010682</v>
       </c>
     </row>
     <row r="23">
@@ -4146,28 +4791,34 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-116349808</v>
+        <v>-164986091</v>
       </c>
       <c r="C28">
-        <v>-256576118.8227396</v>
+        <v>-124509887.14458176</v>
       </c>
       <c r="D28">
-        <v>-267748982.21985447</v>
+        <v>-274570832.1118511</v>
       </c>
       <c r="E28">
-        <v>-103120103</v>
+        <v>-286527293.2746972</v>
       </c>
       <c r="F28">
-        <v>-89769793.55837296</v>
+        <v>-333039169</v>
       </c>
       <c r="G28">
-        <v>-303836787.17496663</v>
+        <v>-110352329.81963877</v>
       </c>
       <c r="H28">
-        <v>-81409003.66796154</v>
+        <v>-96065709.57938685</v>
       </c>
       <c r="I28">
-        <v>-167818382.31578287</v>
+        <v>-325146080.8730118</v>
+      </c>
+      <c r="J28">
+        <v>-87118543.92790002</v>
+      </c>
+      <c r="K28">
+        <v>-179588159.20800146</v>
       </c>
     </row>
     <row r="29">
@@ -4185,39 +4836,45 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>-6619162</v>
+        <v>-369621264</v>
       </c>
       <c r="C31">
-        <v>-298302709.7056806</v>
+        <v>-7083390.405007837</v>
       </c>
       <c r="D31">
-        <v>-311292599.88200474</v>
+        <v>-319223876.3331455</v>
       </c>
       <c r="E31">
-        <v>-28764922</v>
+        <v>-333124799.65804374</v>
       </c>
       <c r="F31">
-        <v>146253125.45300764</v>
+        <v>-300074874</v>
       </c>
       <c r="G31">
-        <v>-71913286.90221323</v>
+        <v>-30782321.46238434</v>
       </c>
       <c r="H31">
-        <v>-405071366.29054576</v>
+        <v>156510444.30340907</v>
       </c>
       <c r="I31">
-        <v>-720140049.0030593</v>
+        <v>-76956854.42291833</v>
+      </c>
+      <c r="J31">
+        <v>-433480647.4484031</v>
+      </c>
+      <c r="K31">
+        <v>-770646361.7856979</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklarda Azalış (Artış)</v>
       </c>
-      <c r="D32">
-        <v>-4773502.067925109</v>
-      </c>
-      <c r="H32">
-        <v>-296723.3014596442</v>
+      <c r="E32">
+        <v>-5108286.932126119</v>
+      </c>
+      <c r="J32">
+        <v>-317533.69784596475</v>
       </c>
     </row>
     <row r="33">
@@ -4225,25 +4882,31 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>1313038</v>
+        <v>932068</v>
       </c>
       <c r="C33">
-        <v>-4574309.172029699</v>
+        <v>1405126.6263932928</v>
       </c>
       <c r="D33">
-        <v>1104531.017698435</v>
+        <v>-4895123.8387419</v>
       </c>
       <c r="E33">
-        <v>-227269</v>
+        <v>1181996.2123299954</v>
       </c>
       <c r="F33">
-        <v>-293552.9855572346</v>
+        <v>258488</v>
       </c>
       <c r="G33">
-        <v>-307003.44417408726</v>
+        <v>-243208.28738679097</v>
+      </c>
+      <c r="H33">
+        <v>-314141.0349614528</v>
       </c>
       <c r="I33">
-        <v>-692902.747056664</v>
+        <v>-328534.8282406578</v>
+      </c>
+      <c r="K33">
+        <v>-741498.7985042133</v>
       </c>
     </row>
     <row r="34">
@@ -4266,28 +4929,34 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>311395101</v>
+        <v>264000408</v>
       </c>
       <c r="C37">
-        <v>-274823295.1113331</v>
+        <v>333234489.5909552</v>
       </c>
       <c r="D37">
-        <v>-286790750.1559648</v>
+        <v>-294097756.13049716</v>
       </c>
       <c r="E37">
-        <v>94711832</v>
+        <v>-306904536.84314734</v>
       </c>
       <c r="F37">
-        <v>905861.9226949204</v>
+        <v>30640114</v>
       </c>
       <c r="G37">
-        <v>62715859.33849004</v>
+        <v>101354353.01772554</v>
       </c>
       <c r="H37">
-        <v>29070643.582796175</v>
+        <v>969393.6560971239</v>
       </c>
       <c r="I37">
-        <v>194484320.9287936</v>
+        <v>67114374.33924136</v>
+      </c>
+      <c r="J37">
+        <v>31109484.527162362</v>
+      </c>
+      <c r="K37">
+        <v>208124287.15167895</v>
       </c>
     </row>
     <row r="38">
@@ -4300,16 +4969,22 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>82099</v>
+        <v>-4151888</v>
       </c>
       <c r="C39">
-        <v>-4023192.503792115</v>
-      </c>
-      <c r="E39">
-        <v>-7738296</v>
+        <v>87856.93247283243</v>
+      </c>
+      <c r="D39">
+        <v>-4305355.14599288</v>
       </c>
       <c r="F39">
-        <v>-1090871.4788936414</v>
+        <v>-11762309</v>
+      </c>
+      <c r="G39">
+        <v>-8281013.765414795</v>
+      </c>
+      <c r="H39">
+        <v>-1167378.675229875</v>
       </c>
     </row>
     <row r="40">
@@ -4317,28 +4992,34 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>-414349757</v>
+        <v>-58834470</v>
       </c>
       <c r="C40">
-        <v>341652335.066505</v>
+        <v>-443409768.94826394</v>
       </c>
       <c r="D40">
-        <v>356529927.72809464</v>
+        <v>365613784.9562534</v>
       </c>
       <c r="E40">
-        <v>-213260189</v>
+        <v>381534802.9202674</v>
       </c>
       <c r="F40">
-        <v>-201476886.76805344</v>
+        <v>-31785074</v>
       </c>
       <c r="G40">
-        <v>-281283697.95160323</v>
+        <v>-228216982.23019135</v>
       </c>
       <c r="H40">
-        <v>240145769.03654376</v>
+        <v>-215607269.7062982</v>
       </c>
       <c r="I40">
-        <v>344578659.89169776</v>
+        <v>-301011252.9585329</v>
+      </c>
+      <c r="J40">
+        <v>256988155.9322286</v>
+      </c>
+      <c r="K40">
+        <v>368745344.6897524</v>
       </c>
     </row>
     <row r="41">
@@ -4351,16 +5032,22 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>-284941</v>
+        <v>759996</v>
       </c>
       <c r="C42">
-        <v>1131308.6876634595</v>
-      </c>
-      <c r="E42">
-        <v>12151794</v>
+        <v>-304925.0562825533</v>
+      </c>
+      <c r="D42">
+        <v>1210651.907793971</v>
       </c>
       <c r="F42">
-        <v>564830.1277224257</v>
+        <v>1168001</v>
+      </c>
+      <c r="G42">
+        <v>13004048.099023987</v>
+      </c>
+      <c r="H42">
+        <v>604443.9322029558</v>
       </c>
     </row>
     <row r="43">
@@ -4373,28 +5060,34 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>2666317</v>
+        <v>5300195</v>
       </c>
       <c r="C44">
-        <v>411707.50102878024</v>
+        <v>2853316.515672117</v>
       </c>
       <c r="D44">
-        <v>429635.5769336942</v>
+        <v>440582.20095791825</v>
       </c>
       <c r="E44">
-        <v>58434245</v>
+        <v>459767.6448018852</v>
       </c>
       <c r="F44">
-        <v>228260.54412940718</v>
+        <v>387856</v>
       </c>
       <c r="G44">
-        <v>337443.3186942033</v>
+        <v>62532473.19779712</v>
       </c>
       <c r="H44">
-        <v>-400276.31685862027</v>
+        <v>244269.37248674541</v>
       </c>
       <c r="I44">
-        <v>467201.78459647053</v>
+        <v>361109.5733678253</v>
+      </c>
+      <c r="J44">
+        <v>-428349.30194913305</v>
+      </c>
+      <c r="K44">
+        <v>499968.52142509545</v>
       </c>
     </row>
     <row r="45">
@@ -4412,16 +5105,22 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
-        <v>-3699867</v>
+        <v>9109309</v>
       </c>
       <c r="C47">
-        <v>-8237999.296877801</v>
-      </c>
-      <c r="E47">
-        <v>825551</v>
+        <v>-3959353.526565014</v>
+      </c>
+      <c r="D47">
+        <v>-8815763.260661323</v>
       </c>
       <c r="F47">
-        <v>-30491594.356080335</v>
+        <v>-579505</v>
+      </c>
+      <c r="G47">
+        <v>883450.2059693696</v>
+      </c>
+      <c r="H47">
+        <v>-32630092.282867614</v>
       </c>
     </row>
     <row r="48">
@@ -4429,25 +5128,31 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>-6852636</v>
+        <v>-12480445</v>
       </c>
       <c r="C48">
-        <v>-9809964.288223526</v>
+        <v>-7333238.873955839</v>
       </c>
       <c r="D48">
-        <v>-34387035.563774414</v>
+        <v>-10497976.467817536</v>
       </c>
       <c r="E48">
-        <v>-19252849</v>
+        <v>-36798736.42148401</v>
       </c>
       <c r="F48">
-        <v>-4368966.017342702</v>
+        <v>-21291866</v>
       </c>
       <c r="G48">
-        <v>-13386101.534160342</v>
+        <v>-20603128.594777517</v>
+      </c>
+      <c r="H48">
+        <v>-4675379.144225597</v>
       </c>
       <c r="I48">
-        <v>13514559.301209208</v>
+        <v>-14324922.575929105</v>
+      </c>
+      <c r="K48">
+        <v>14462389.60190047</v>
       </c>
     </row>
     <row r="49">
@@ -4455,16 +5160,22 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>-67676701</v>
+        <v>-18444631</v>
       </c>
       <c r="C49">
-        <v>4927284.94784383</v>
-      </c>
-      <c r="E49">
-        <v>-66760558</v>
+        <v>-72423139.74276264</v>
+      </c>
+      <c r="D49">
+        <v>5272855.222805625</v>
       </c>
       <c r="F49">
-        <v>164413489.44672397</v>
+        <v>-173142834</v>
+      </c>
+      <c r="G49">
+        <v>-71442743.9561336</v>
+      </c>
+      <c r="H49">
+        <v>175944467.53241298</v>
       </c>
     </row>
     <row r="50">
@@ -4492,28 +5203,34 @@
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
       <c r="B54">
-        <v>-41509236</v>
+        <v>-73198421</v>
       </c>
       <c r="C54">
-        <v>-100273602.55492093</v>
+        <v>-44420445.3677982</v>
       </c>
       <c r="D54">
-        <v>-104640116.83195451</v>
+        <v>-107306192.87050177</v>
       </c>
       <c r="E54">
-        <v>-15840401</v>
+        <v>-111978948.32402736</v>
       </c>
       <c r="F54">
-        <v>-121298126.33184494</v>
+        <v>-43628201</v>
       </c>
       <c r="G54">
-        <v>-109446983.69618683</v>
+        <v>-16951351.916583482</v>
       </c>
       <c r="H54">
-        <v>-187326919.57062724</v>
+        <v>-129805250.9070512</v>
       </c>
       <c r="I54">
-        <v>-159335754.79732603</v>
+        <v>-117122940.05957535</v>
+      </c>
+      <c r="J54">
+        <v>-200464908.50144714</v>
+      </c>
+      <c r="K54">
+        <v>-170510610.9664729</v>
       </c>
     </row>
     <row r="55">
@@ -4559,22 +5276,28 @@
         <v>-82298</v>
       </c>
       <c r="C62">
-        <v>-928873.9484329243</v>
+        <v>-88069.88914175767</v>
       </c>
       <c r="D62">
-        <v>-969322.1614231602</v>
+        <v>-994019.6075865072</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>-1037304.6161411778</v>
       </c>
       <c r="F62">
-        <v>-3457703.2232666546</v>
+        <v>0</v>
       </c>
       <c r="G62">
-        <v>-2817072.724039307</v>
+        <v>0</v>
       </c>
       <c r="H62">
-        <v>-7013980.052193166</v>
+        <v>-3700205.8319545123</v>
+      </c>
+      <c r="I62">
+        <v>-3014645.343877264</v>
+      </c>
+      <c r="J62">
+        <v>-7505898.6322772335</v>
       </c>
     </row>
     <row r="63">
@@ -4598,28 +5321,34 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-258011482</v>
+        <v>-319394516</v>
       </c>
       <c r="C67">
-        <v>-66668846.01643772</v>
+        <v>-276106863.0712849</v>
       </c>
       <c r="D67">
-        <v>-69572008.05807272</v>
+        <v>-71344599.84296802</v>
       </c>
       <c r="E67">
-        <v>-10447406</v>
+        <v>-74451372.29390672</v>
       </c>
       <c r="F67">
-        <v>-5614968.393156264</v>
+        <v>-21995856</v>
       </c>
       <c r="G67">
-        <v>-3249500.0716930334</v>
+        <v>-11180124.525977958</v>
       </c>
       <c r="H67">
-        <v>-1976925.8048362632</v>
+        <v>-6008768.668980356</v>
       </c>
       <c r="I67">
-        <v>-5110237.815246438</v>
+        <v>-3477400.557487898</v>
+      </c>
+      <c r="J67">
+        <v>-2115575.5482929084</v>
+      </c>
+      <c r="K67">
+        <v>-5468639.309300004</v>
       </c>
     </row>
     <row r="68">
@@ -4651,10 +5380,10 @@
       <c r="A73" t="str">
         <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
       </c>
-      <c r="C73">
-        <v>-7246648.887022002</v>
-      </c>
-      <c r="F73">
+      <c r="D73">
+        <v>-7754885.466588122</v>
+      </c>
+      <c r="H73">
         <v>0</v>
       </c>
     </row>
@@ -4673,15 +5402,21 @@
         <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
       <c r="B76">
-        <v>-257068770</v>
+        <v>-299116288</v>
       </c>
       <c r="C76">
-        <v>-6194562.883413444</v>
-      </c>
-      <c r="E76">
-        <v>0</v>
+        <v>-275098034.8940193</v>
+      </c>
+      <c r="D76">
+        <v>-6629012.447737111</v>
       </c>
       <c r="F76">
+        <v>-7754886</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
         <v>0</v>
       </c>
     </row>
@@ -4689,14 +5424,20 @@
       <c r="A77" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C77">
+      <c r="B77">
         <v>0</v>
       </c>
       <c r="D77">
-        <v>13952.251067910878</v>
+        <v>0</v>
+      </c>
+      <c r="E77">
+        <v>14930.778449401943</v>
       </c>
       <c r="F77">
-        <v>696175.4022089605</v>
+        <v>16139</v>
+      </c>
+      <c r="H77">
+        <v>745000.9781010682</v>
       </c>
     </row>
     <row r="78">
@@ -4704,25 +5445,31 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-942712</v>
+        <v>-20278228</v>
       </c>
       <c r="C78">
-        <v>-53227634.24600227</v>
+        <v>-1008828.1772656037</v>
       </c>
       <c r="D78">
-        <v>-55545485.10487297</v>
+        <v>-56960701.92864279</v>
       </c>
       <c r="E78">
-        <v>-10447406</v>
+        <v>-59441112.97372129</v>
       </c>
       <c r="F78">
-        <v>-6311143.795365224</v>
+        <v>-14257109</v>
       </c>
       <c r="G78">
-        <v>-3249500.0716930334</v>
+        <v>-11180124.525977958</v>
+      </c>
+      <c r="H78">
+        <v>-6753769.647081424</v>
       </c>
       <c r="I78">
-        <v>-5110237.815246438</v>
+        <v>-3477400.557487898</v>
+      </c>
+      <c r="K78">
+        <v>-5468639.309300004</v>
       </c>
     </row>
     <row r="79">
@@ -4836,28 +5583,34 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>506551683</v>
+        <v>593335973</v>
       </c>
       <c r="C101">
-        <v>39148073.151232116</v>
+        <v>542078186.1816906</v>
       </c>
       <c r="D101">
-        <v>40852815.06614075</v>
+        <v>41893684.68908639</v>
       </c>
       <c r="E101">
-        <v>-100975960</v>
+        <v>43717986.99851446</v>
       </c>
       <c r="F101">
-        <v>-207197573.80718696</v>
+        <v>31590617</v>
       </c>
       <c r="G101">
-        <v>-161113089.35348776</v>
+        <v>-108057809.46295847</v>
       </c>
       <c r="H101">
-        <v>-37572248.97978582</v>
+        <v>-221729171.4943268</v>
       </c>
       <c r="I101">
-        <v>-66305750.75952724</v>
+        <v>-172412597.1305228</v>
+      </c>
+      <c r="J101">
+        <v>-40207341.642035715</v>
+      </c>
+      <c r="K101">
+        <v>-70956039.25797199</v>
       </c>
     </row>
     <row r="102">
@@ -4875,9 +5628,15 @@
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B104">
-        <v>578275441</v>
-      </c>
-      <c r="E104">
+        <v>618832219</v>
+      </c>
+      <c r="C104">
+        <v>618832219.2795819</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
         <v>0</v>
       </c>
     </row>
@@ -4890,36 +5649,36 @@
       <c r="A106" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
-      <c r="G106">
-        <v>-108441341.0048522</v>
-      </c>
       <c r="I106">
-        <v>-91668184.44293045</v>
+        <v>-116046767.60894401</v>
+      </c>
+      <c r="K106">
+        <v>-98097242.23814769</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="D107">
-        <v>-75244146.67756633</v>
-      </c>
-      <c r="G107">
-        <v>-49791180.17236266</v>
+      <c r="E107">
+        <v>-80521320.76671876</v>
       </c>
       <c r="I107">
-        <v>30196487.574600086</v>
+        <v>-53283235.53448762</v>
+      </c>
+      <c r="K107">
+        <v>32314288.47803704</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
         <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="B108">
-        <v>0</v>
-      </c>
-      <c r="E108">
-        <v>-24490995</v>
+      <c r="C108">
+        <v>0</v>
+      </c>
+      <c r="G108">
+        <v>-26208646.803340804</v>
       </c>
     </row>
     <row r="109">
@@ -4927,42 +5686,48 @@
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B109">
-        <v>-91868253</v>
+        <v>-23362761</v>
       </c>
       <c r="C109">
-        <v>142697855.51024938</v>
+        <v>-98311342.40633972</v>
       </c>
       <c r="D109">
-        <v>123354249.51102915</v>
+        <v>152705829.00622392</v>
       </c>
       <c r="E109">
-        <v>8937890</v>
+        <v>132005578.25950877</v>
+      </c>
+      <c r="F109">
+        <v>130355615</v>
       </c>
       <c r="G109">
-        <v>-2880567.0758508425</v>
+        <v>9564740.108644493</v>
       </c>
       <c r="I109">
-        <v>-4834053.891196885</v>
+        <v>-3082592.809492099</v>
+      </c>
+      <c r="K109">
+        <v>-5173085.497861332</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
-      <c r="D110">
-        <v>-561851.2852552884</v>
-      </c>
-      <c r="F110">
-        <v>-85419028.52160154</v>
-      </c>
-      <c r="G110">
-        <v>-2760364.6749595175</v>
+      <c r="E110">
+        <v>-601256.17155444</v>
       </c>
       <c r="H110">
-        <v>114968039.87145227</v>
+        <v>-91409807.92357147</v>
       </c>
       <c r="I110">
-        <v>-4632334.4262935165</v>
+        <v>-2953960.13164972</v>
+      </c>
+      <c r="J110">
+        <v>123031210.06979486</v>
+      </c>
+      <c r="K110">
+        <v>-4957218.637041211</v>
       </c>
     </row>
     <row r="111">
@@ -4980,16 +5745,22 @@
         <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B113">
-        <v>-6566101</v>
+        <v>3404372</v>
       </c>
       <c r="C113">
-        <v>-24491040.280323405</v>
-      </c>
-      <c r="E113">
-        <v>-6813898</v>
+        <v>-7026608.024053855</v>
+      </c>
+      <c r="D113">
+        <v>-26208695.259355076</v>
       </c>
       <c r="F113">
-        <v>-13339154.228591269</v>
+        <v>-14307671</v>
+      </c>
+      <c r="G113">
+        <v>-7291784.022494402</v>
+      </c>
+      <c r="H113">
+        <v>-14274682.66734114</v>
       </c>
     </row>
     <row r="114">
@@ -5001,8 +5772,8 @@
       <c r="A115" t="str">
         <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
-      <c r="G115">
-        <v>-158894473.45392403</v>
+      <c r="I115">
+        <v>-170038380.79084602</v>
       </c>
     </row>
     <row r="116">
@@ -5015,19 +5786,25 @@
         <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
       <c r="B117">
-        <v>0</v>
+        <v>-17000000</v>
       </c>
       <c r="C117">
-        <v>-78520336.38546105</v>
-      </c>
-      <c r="E117">
-        <v>-78520905</v>
+        <v>0</v>
+      </c>
+      <c r="D117">
+        <v>-84027282.81174603</v>
       </c>
       <c r="F117">
-        <v>-108439391.05699414</v>
+        <v>-84028101</v>
+      </c>
+      <c r="G117">
+        <v>-84027891.30550542</v>
       </c>
       <c r="H117">
-        <v>-152263986.08160803</v>
+        <v>-116044680.9034142</v>
+      </c>
+      <c r="J117">
+        <v>-162942870.7196937</v>
       </c>
     </row>
     <row r="118">
@@ -5035,18 +5812,24 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
-        <v>-2289404</v>
+        <v>-17537857</v>
       </c>
       <c r="C118">
-        <v>-538405.6932328173</v>
+        <v>-2449969.093789601</v>
       </c>
       <c r="D118">
-        <v>-9303984.731296264</v>
+        <v>-576166.2460364214</v>
       </c>
       <c r="E118">
-        <v>-88052</v>
+        <v>-9956510.533206979</v>
       </c>
       <c r="F118">
+        <v>-429226</v>
+      </c>
+      <c r="G118">
+        <v>-94227.44026233986</v>
+      </c>
+      <c r="H118">
         <v>0</v>
       </c>
     </row>
@@ -5077,7 +5860,13 @@
       <c r="B123">
         <v>29000000</v>
       </c>
-      <c r="E123">
+      <c r="C123">
+        <v>31033886.42629192</v>
+      </c>
+      <c r="F123">
+        <v>0</v>
+      </c>
+      <c r="G123">
         <v>0</v>
       </c>
     </row>
@@ -5091,19 +5880,25 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>139271966</v>
+        <v>182216107</v>
       </c>
       <c r="C125">
-        <v>-123795964.42071562</v>
+        <v>149039668.11070308</v>
       </c>
       <c r="D125">
-        <v>-98498.77696101449</v>
+        <v>-132478272.40916426</v>
       </c>
       <c r="E125">
-        <v>-194024325</v>
+        <v>-105406.89163230285</v>
       </c>
       <c r="F125">
-        <v>-173154882.30873084</v>
+        <v>-207176274</v>
+      </c>
+      <c r="G125">
+        <v>-207632029.8616535</v>
+      </c>
+      <c r="H125">
+        <v>-185298929.3698999</v>
       </c>
     </row>
     <row r="126">
@@ -5111,15 +5906,21 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
       <c r="B126">
-        <v>-1736390</v>
+        <v>-469063</v>
       </c>
       <c r="C126">
-        <v>-94388.7006349125</v>
-      </c>
-      <c r="E126">
-        <v>0</v>
+        <v>-1858170.0017844492</v>
+      </c>
+      <c r="D126">
+        <v>-101008.55915272905</v>
       </c>
       <c r="F126">
+        <v>0</v>
+      </c>
+      <c r="G126">
+        <v>0</v>
+      </c>
+      <c r="H126">
         <v>0</v>
       </c>
     </row>
@@ -5128,28 +5929,34 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>137535576</v>
+        <v>181747044</v>
       </c>
       <c r="C127">
-        <v>-123890353.12135053</v>
+        <v>147181498.10891864</v>
       </c>
       <c r="D127">
-        <v>-129285282.22345163</v>
+        <v>-132579280.96831699</v>
       </c>
       <c r="E127">
-        <v>-194024325</v>
+        <v>-138352578.1073688</v>
       </c>
       <c r="F127">
-        <v>-173154882.30873084</v>
+        <v>-207176274</v>
       </c>
       <c r="G127">
-        <v>-214735621.05340835</v>
+        <v>-207632029.8616535</v>
       </c>
       <c r="H127">
-        <v>430240134.49796945</v>
+        <v>-185298929.3698999</v>
       </c>
       <c r="I127">
-        <v>76670052.65130469</v>
+        <v>-229795892.2569219</v>
+      </c>
+      <c r="J127">
+        <v>460414602.41526014</v>
+      </c>
+      <c r="K127">
+        <v>82047231.2509797</v>
       </c>
     </row>
     <row r="128">
@@ -5157,16 +5964,22 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>86895461</v>
+        <v>92990035</v>
       </c>
       <c r="C128">
-        <v>236450567.22610682</v>
-      </c>
-      <c r="E128">
-        <v>236451662</v>
+        <v>92989788.53911306</v>
+      </c>
+      <c r="D128">
+        <v>253033794.78370005</v>
       </c>
       <c r="F128">
-        <v>496538925.0880824</v>
+        <v>253034580</v>
+      </c>
+      <c r="G128">
+        <v>253034966.33848155</v>
+      </c>
+      <c r="H128">
+        <v>531363193.3591938</v>
       </c>
     </row>
     <row r="129">
@@ -5174,28 +5987,34 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>204310994</v>
+        <v>251155812</v>
       </c>
       <c r="C129">
-        <v>86895622.13542902</v>
-      </c>
-      <c r="E129">
-        <v>26323317</v>
+        <v>218640144.25651067</v>
+      </c>
+      <c r="D129">
+        <v>92989960.97561663</v>
       </c>
       <c r="F129">
-        <v>236450567.22610682</v>
+        <v>24874182</v>
+      </c>
+      <c r="G129">
+        <v>28169476.901423424</v>
+      </c>
+      <c r="H129">
+        <v>253033794.78370005</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -5206,6 +6025,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5213,27 +6034,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -5247,16 +6074,25 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>-109268235</v>
+        <v>25206304.999702603</v>
       </c>
       <c r="C3">
-        <v>4192398.8990486413</v>
+        <v>-116931654.9997026</v>
+      </c>
+      <c r="D3">
+        <v>4486428.665061623</v>
       </c>
       <c r="E3">
-        <v>-82600959</v>
+        <v>109257249.07965574</v>
       </c>
       <c r="F3">
-        <v>-22233364.900386184</v>
+        <v>-128376939.12728292</v>
+      </c>
+      <c r="G3">
+        <v>-88394095.87271708</v>
+      </c>
+      <c r="H3">
+        <v>-23792680.041134134</v>
       </c>
     </row>
     <row r="4">
@@ -5264,16 +6100,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>-4892536</v>
+        <v>15258283.191742916</v>
       </c>
       <c r="C4">
-        <v>-3963443.988610834</v>
+        <v>-5235669.191742916</v>
+      </c>
+      <c r="D4">
+        <v>-4241416.22756958</v>
       </c>
       <c r="E4">
-        <v>-23880863</v>
+        <v>62666905.93512282</v>
       </c>
       <c r="F4">
-        <v>4658106.310512349</v>
+        <v>64531067.79668403</v>
+      </c>
+      <c r="G4">
+        <v>-25555723.79668403</v>
+      </c>
+      <c r="H4">
+        <v>4984798.00696668</v>
       </c>
     </row>
     <row r="5">
@@ -5281,16 +6126,25 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>53565643</v>
+        <v>79196429.40643796</v>
       </c>
       <c r="C5">
-        <v>-7423982.999479204</v>
+        <v>57322416.59356203</v>
+      </c>
+      <c r="D5">
+        <v>-7944656.732295185</v>
       </c>
       <c r="E5">
-        <v>60240408</v>
+        <v>69466519.35939866</v>
       </c>
       <c r="F5">
-        <v>-116202635.27238059</v>
+        <v>56455681.33981079</v>
+      </c>
+      <c r="G5">
+        <v>64465309.66018921</v>
+      </c>
+      <c r="H5">
+        <v>-124352392.60272008</v>
       </c>
     </row>
     <row r="6">
@@ -5298,16 +6152,25 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>8302570</v>
+        <v>8017573.433574535</v>
       </c>
       <c r="C6">
-        <v>-1553890.5593092516</v>
+        <v>8884862.566425465</v>
+      </c>
+      <c r="D6">
+        <v>-1662871.1426376104</v>
       </c>
       <c r="E6">
-        <v>8004901</v>
+        <v>21868066.717311688</v>
       </c>
       <c r="F6">
-        <v>11520907.081337672</v>
+        <v>9415042.155596185</v>
+      </c>
+      <c r="G6">
+        <v>8566316.844403815</v>
+      </c>
+      <c r="H6">
+        <v>12328914.547934333</v>
       </c>
     </row>
     <row r="7">
@@ -5315,16 +6178,25 @@
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B7">
-        <v>-166258</v>
+        <v>2180586.341015946</v>
       </c>
       <c r="C7">
-        <v>-524069.3948723208</v>
+        <v>-177918.34101594627</v>
+      </c>
+      <c r="D7">
+        <v>-560824.4855159707</v>
       </c>
       <c r="E7">
-        <v>7066461</v>
+        <v>3835251.5884537585</v>
       </c>
       <c r="F7">
-        <v>-6388556.285161375</v>
+        <v>2042397.720350992</v>
+      </c>
+      <c r="G7">
+        <v>7562060.279649008</v>
+      </c>
+      <c r="H7">
+        <v>-6836611.38557488</v>
       </c>
     </row>
     <row r="8">
@@ -5332,16 +6204,25 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>7084232</v>
+        <v>22272405.368775763</v>
       </c>
       <c r="C8">
-        <v>-238586.90456960537</v>
+        <v>7581077.631224236</v>
+      </c>
+      <c r="D8">
+        <v>-255319.96204185113</v>
       </c>
       <c r="E8">
-        <v>4665848</v>
+        <v>-574669.7244832609</v>
       </c>
       <c r="F8">
-        <v>1403910.7379669715</v>
+        <v>1700130.347781334</v>
+      </c>
+      <c r="G8">
+        <v>4993082.652218666</v>
+      </c>
+      <c r="H8">
+        <v>1502372.6343006436</v>
       </c>
     </row>
     <row r="9">
@@ -5364,16 +6245,25 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>2765259</v>
+        <v>-2773.71535453666</v>
       </c>
       <c r="C12">
-        <v>-253674.79118464887</v>
+        <v>2959197.7153545367</v>
+      </c>
+      <c r="D12">
+        <v>-271466.02271854226</v>
       </c>
       <c r="E12">
-        <v>1475117</v>
+        <v>3352966.7082191445</v>
       </c>
       <c r="F12">
-        <v>2376009.264201578</v>
+        <v>1573932.122638191</v>
+      </c>
+      <c r="G12">
+        <v>1578572.877361809</v>
+      </c>
+      <c r="H12">
+        <v>2542648.332863766</v>
       </c>
     </row>
     <row r="13">
@@ -5416,16 +6306,25 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>28709366</v>
+        <v>35262701.902936324</v>
       </c>
       <c r="C20">
-        <v>-5175401.507295385</v>
+        <v>30722869.09706368</v>
+      </c>
+      <c r="D20">
+        <v>-5538373.192685008</v>
       </c>
       <c r="E20">
-        <v>28694480</v>
+        <v>59078470.43265121</v>
       </c>
       <c r="F20">
-        <v>12695898.122372195</v>
+        <v>42937381.917879134</v>
+      </c>
+      <c r="G20">
+        <v>30706939.08212086</v>
+      </c>
+      <c r="H20">
+        <v>13586312.427912816</v>
       </c>
     </row>
     <row r="21">
@@ -5437,8 +6336,11 @@
       <c r="A22" t="str">
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C22">
-        <v>-27569.973835116252</v>
+      <c r="D22">
+        <v>-29503.566785339266</v>
+      </c>
+      <c r="E22">
+        <v>71063.47409266722</v>
       </c>
     </row>
     <row r="23">
@@ -5471,16 +6373,25 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-116349808</v>
+        <v>-40476203.855418235</v>
       </c>
       <c r="C28">
-        <v>11172863.397114873</v>
+        <v>-124509887.14458176</v>
+      </c>
+      <c r="D28">
+        <v>11956461.162846088</v>
       </c>
       <c r="E28">
-        <v>-103120103</v>
+        <v>46511875.725302815</v>
       </c>
       <c r="F28">
-        <v>214066993.61659366</v>
+        <v>-222686839.1803612</v>
+      </c>
+      <c r="G28">
+        <v>-110352329.81963877</v>
+      </c>
+      <c r="H28">
+        <v>229080371.293625</v>
       </c>
     </row>
     <row r="29">
@@ -5498,16 +6409,25 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>-6619162</v>
+        <v>-362537873.59499216</v>
       </c>
       <c r="C31">
-        <v>12989890.17632413</v>
+        <v>-7083390.405007837</v>
+      </c>
+      <c r="D31">
+        <v>13900923.324898243</v>
       </c>
       <c r="E31">
-        <v>-28764922</v>
+        <v>-33049925.658043742</v>
       </c>
       <c r="F31">
-        <v>218166412.35522085</v>
+        <v>-269292552.53761566</v>
+      </c>
+      <c r="G31">
+        <v>-30782321.46238434</v>
+      </c>
+      <c r="H31">
+        <v>233467298.72632742</v>
       </c>
     </row>
     <row r="32">
@@ -5520,16 +6440,25 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>1313038</v>
+        <v>-473058.6263932928</v>
       </c>
       <c r="C33">
-        <v>-5678840.189728134</v>
+        <v>1405126.6263932928</v>
+      </c>
+      <c r="D33">
+        <v>-6077120.051071895</v>
       </c>
       <c r="E33">
-        <v>-227269</v>
+        <v>923508.2123299954</v>
       </c>
       <c r="F33">
-        <v>13450.458616852644</v>
+        <v>501696.28738679097</v>
+      </c>
+      <c r="G33">
+        <v>-243208.28738679097</v>
+      </c>
+      <c r="H33">
+        <v>14393.793279204983</v>
       </c>
     </row>
     <row r="34">
@@ -5552,16 +6481,25 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>311395101</v>
+        <v>-69234081.5909552</v>
       </c>
       <c r="C37">
-        <v>11967455.04463172</v>
+        <v>333234489.5909552</v>
+      </c>
+      <c r="D37">
+        <v>12806780.71265018</v>
       </c>
       <c r="E37">
-        <v>94711832</v>
+        <v>-337544650.84314734</v>
       </c>
       <c r="F37">
-        <v>-61809997.41579512</v>
+        <v>-70714239.01772554</v>
+      </c>
+      <c r="G37">
+        <v>101354353.01772554</v>
+      </c>
+      <c r="H37">
+        <v>-66144980.683144234</v>
       </c>
     </row>
     <row r="38">
@@ -5574,10 +6512,16 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>82099</v>
-      </c>
-      <c r="E39">
-        <v>-7738296</v>
+        <v>-4239744.9324728325</v>
+      </c>
+      <c r="C39">
+        <v>87856.93247283243</v>
+      </c>
+      <c r="F39">
+        <v>-3481295.234585205</v>
+      </c>
+      <c r="G39">
+        <v>-8281013.765414795</v>
       </c>
     </row>
     <row r="40">
@@ -5585,16 +6529,25 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>-414349757</v>
+        <v>384575298.94826394</v>
       </c>
       <c r="C40">
-        <v>-14877592.661589622</v>
+        <v>-443409768.94826394</v>
+      </c>
+      <c r="D40">
+        <v>-15921017.964013994</v>
       </c>
       <c r="E40">
-        <v>-213260189</v>
+        <v>413319876.9202674</v>
       </c>
       <c r="F40">
-        <v>79806811.18354979</v>
+        <v>196431908.23019135</v>
+      </c>
+      <c r="G40">
+        <v>-228216982.23019135</v>
+      </c>
+      <c r="H40">
+        <v>85403983.25223473</v>
       </c>
     </row>
     <row r="41">
@@ -5607,10 +6560,16 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>-284941</v>
-      </c>
-      <c r="E42">
-        <v>12151794</v>
+        <v>1064921.0562825534</v>
+      </c>
+      <c r="C42">
+        <v>-304925.0562825533</v>
+      </c>
+      <c r="F42">
+        <v>-11836047.099023987</v>
+      </c>
+      <c r="G42">
+        <v>13004048.099023987</v>
       </c>
     </row>
     <row r="43">
@@ -5623,16 +6582,25 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>2666317</v>
+        <v>2446878.484327883</v>
       </c>
       <c r="C44">
-        <v>-17928.075904913945</v>
+        <v>2853316.515672117</v>
+      </c>
+      <c r="D44">
+        <v>-19185.443843966932</v>
       </c>
       <c r="E44">
-        <v>58434245</v>
+        <v>71911.64480188518</v>
       </c>
       <c r="F44">
-        <v>-109182.7745647961</v>
+        <v>-62144617.19779712</v>
+      </c>
+      <c r="G44">
+        <v>62532473.19779712</v>
+      </c>
+      <c r="H44">
+        <v>-116840.20088107989</v>
       </c>
     </row>
     <row r="45">
@@ -5650,10 +6618,16 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
-        <v>-3699867</v>
-      </c>
-      <c r="E47">
-        <v>825551</v>
+        <v>13068662.526565013</v>
+      </c>
+      <c r="C47">
+        <v>-3959353.526565014</v>
+      </c>
+      <c r="F47">
+        <v>-1462955.2059693695</v>
+      </c>
+      <c r="G47">
+        <v>883450.2059693696</v>
       </c>
     </row>
     <row r="48">
@@ -5661,16 +6635,25 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>-6852636</v>
+        <v>-5147206.126044161</v>
       </c>
       <c r="C48">
-        <v>24577071.275550887</v>
+        <v>-7333238.873955839</v>
+      </c>
+      <c r="D48">
+        <v>26300759.95366647</v>
       </c>
       <c r="E48">
-        <v>-19252849</v>
+        <v>-15506870.421484008</v>
       </c>
       <c r="F48">
-        <v>9017135.51681764</v>
+        <v>-688737.405222483</v>
+      </c>
+      <c r="G48">
+        <v>-20603128.594777517</v>
+      </c>
+      <c r="H48">
+        <v>9649543.431703508</v>
       </c>
     </row>
     <row r="49">
@@ -5678,10 +6661,16 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>-67676701</v>
-      </c>
-      <c r="E49">
-        <v>-66760558</v>
+        <v>53978508.74276264</v>
+      </c>
+      <c r="C49">
+        <v>-72423139.74276264</v>
+      </c>
+      <c r="F49">
+        <v>-101700090.0438664</v>
+      </c>
+      <c r="G49">
+        <v>-71442743.9561336</v>
       </c>
     </row>
     <row r="50">
@@ -5709,16 +6698,25 @@
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
       <c r="B54">
-        <v>-41509236</v>
+        <v>-28777975.6322018</v>
       </c>
       <c r="C54">
-        <v>4366514.277033582</v>
+        <v>-44420445.3677982</v>
+      </c>
+      <c r="D54">
+        <v>4672755.453525588</v>
       </c>
       <c r="E54">
-        <v>-15840401</v>
+        <v>-68350747.32402736</v>
       </c>
       <c r="F54">
-        <v>-11851142.635658115</v>
+        <v>-26676849.083416518</v>
+      </c>
+      <c r="G54">
+        <v>-16951351.916583482</v>
+      </c>
+      <c r="H54">
+        <v>-12682310.847475857</v>
       </c>
     </row>
     <row r="55">
@@ -5761,16 +6759,25 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
       <c r="B62">
-        <v>-82298</v>
+        <v>5771.889141757667</v>
       </c>
       <c r="C62">
-        <v>40448.21299023589</v>
+        <v>-88069.88914175767</v>
+      </c>
+      <c r="D62">
+        <v>43285.00855467061</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>-1037304.6161411778</v>
       </c>
       <c r="F62">
-        <v>-640630.4992273478</v>
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>-685560.4880772484</v>
       </c>
     </row>
     <row r="63">
@@ -5794,16 +6801,25 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-258011482</v>
+        <v>-43287652.92871511</v>
       </c>
       <c r="C67">
-        <v>2903162.041634999</v>
+        <v>-276106863.0712849</v>
+      </c>
+      <c r="D67">
+        <v>3106772.4509387016</v>
       </c>
       <c r="E67">
-        <v>-10447406</v>
+        <v>-52455516.29390672</v>
       </c>
       <c r="F67">
-        <v>-2365468.3214632305</v>
+        <v>-10815731.474022042</v>
+      </c>
+      <c r="G67">
+        <v>-11180124.525977958</v>
+      </c>
+      <c r="H67">
+        <v>-2531368.1114924583</v>
       </c>
     </row>
     <row r="68">
@@ -5851,9 +6867,15 @@
         <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
       <c r="B76">
-        <v>-257068770</v>
-      </c>
-      <c r="E76">
+        <v>-24018253.105980694</v>
+      </c>
+      <c r="C76">
+        <v>-275098034.8940193</v>
+      </c>
+      <c r="F76">
+        <v>-7754886</v>
+      </c>
+      <c r="G76">
         <v>0</v>
       </c>
     </row>
@@ -5861,8 +6883,11 @@
       <c r="A77" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C77">
-        <v>-13952.251067910878</v>
+      <c r="D77">
+        <v>-14930.778449401943</v>
+      </c>
+      <c r="E77">
+        <v>-1208.2215505980566</v>
       </c>
     </row>
     <row r="78">
@@ -5870,16 +6895,25 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-942712</v>
+        <v>-19269399.822734397</v>
       </c>
       <c r="C78">
-        <v>2317850.8588707</v>
+        <v>-1008828.1772656037</v>
+      </c>
+      <c r="D78">
+        <v>2480411.045078501</v>
       </c>
       <c r="E78">
-        <v>-10447406</v>
+        <v>-45184003.97372129</v>
       </c>
       <c r="F78">
-        <v>-3061643.72367219</v>
+        <v>-3076984.474022042</v>
+      </c>
+      <c r="G78">
+        <v>-11180124.525977958</v>
+      </c>
+      <c r="H78">
+        <v>-3276369.0895935255</v>
       </c>
     </row>
     <row r="79">
@@ -5993,16 +7027,25 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>506551683</v>
+        <v>51257786.81830943</v>
       </c>
       <c r="C101">
-        <v>-1704741.9149086326</v>
+        <v>542078186.1816906</v>
+      </c>
+      <c r="D101">
+        <v>-1824302.309428066</v>
       </c>
       <c r="E101">
-        <v>-100975960</v>
+        <v>12127369.998514459</v>
       </c>
       <c r="F101">
-        <v>-46084484.4536992</v>
+        <v>139648426.46295846</v>
+      </c>
+      <c r="G101">
+        <v>-108057809.46295847</v>
+      </c>
+      <c r="H101">
+        <v>-49316574.36380401</v>
       </c>
     </row>
     <row r="102">
@@ -6020,9 +7063,15 @@
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B104">
-        <v>578275441</v>
-      </c>
-      <c r="E104">
+        <v>-0.2795819044113159</v>
+      </c>
+      <c r="C104">
+        <v>618832219.2795819</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
         <v>0</v>
       </c>
     </row>
@@ -6045,11 +7094,11 @@
       <c r="A108" t="str">
         <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="B108">
-        <v>0</v>
-      </c>
-      <c r="E108">
-        <v>-24490995</v>
+      <c r="C108">
+        <v>0</v>
+      </c>
+      <c r="G108">
+        <v>-26208646.803340804</v>
       </c>
     </row>
     <row r="109">
@@ -6057,21 +7106,30 @@
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B109">
-        <v>-91868253</v>
+        <v>74948581.40633972</v>
       </c>
       <c r="C109">
-        <v>19343605.999220222</v>
+        <v>-98311342.40633972</v>
+      </c>
+      <c r="D109">
+        <v>20700250.746715143</v>
       </c>
       <c r="E109">
-        <v>8937890</v>
+        <v>1649963.2595087737</v>
+      </c>
+      <c r="F109">
+        <v>120790874.89135551</v>
+      </c>
+      <c r="G109">
+        <v>9564740.108644493</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
-      <c r="F110">
-        <v>-82658663.84664203</v>
+      <c r="H110">
+        <v>-88455847.79192175</v>
       </c>
     </row>
     <row r="111">
@@ -6089,10 +7147,16 @@
         <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B113">
-        <v>-6566101</v>
-      </c>
-      <c r="E113">
-        <v>-6813898</v>
+        <v>10430980.024053855</v>
+      </c>
+      <c r="C113">
+        <v>-7026608.024053855</v>
+      </c>
+      <c r="F113">
+        <v>-7015886.977505598</v>
+      </c>
+      <c r="G113">
+        <v>-7291784.022494402</v>
       </c>
     </row>
     <row r="114">
@@ -6115,10 +7179,16 @@
         <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
       <c r="B117">
-        <v>0</v>
-      </c>
-      <c r="E117">
-        <v>-78520905</v>
+        <v>-17000000</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+      <c r="F117">
+        <v>-209.69449457526207</v>
+      </c>
+      <c r="G117">
+        <v>-84027891.30550542</v>
       </c>
     </row>
     <row r="118">
@@ -6126,13 +7196,22 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
-        <v>-2289404</v>
+        <v>-15087887.9062104</v>
       </c>
       <c r="C118">
-        <v>8765579.038063446</v>
+        <v>-2449969.093789601</v>
+      </c>
+      <c r="D118">
+        <v>9380344.287170557</v>
       </c>
       <c r="E118">
-        <v>-88052</v>
+        <v>-9527284.533206979</v>
+      </c>
+      <c r="F118">
+        <v>-334998.5597376601</v>
+      </c>
+      <c r="G118">
+        <v>-94227.44026233986</v>
       </c>
     </row>
     <row r="119">
@@ -6160,9 +7239,15 @@
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
       <c r="B123">
-        <v>29000000</v>
-      </c>
-      <c r="E123">
+        <v>-2033886.4262919202</v>
+      </c>
+      <c r="C123">
+        <v>31033886.42629192</v>
+      </c>
+      <c r="F123">
+        <v>0</v>
+      </c>
+      <c r="G123">
         <v>0</v>
       </c>
     </row>
@@ -6176,13 +7261,22 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>139271966</v>
+        <v>33176438.88929692</v>
       </c>
       <c r="C125">
-        <v>-123697465.6437546</v>
+        <v>149039668.11070308</v>
+      </c>
+      <c r="D125">
+        <v>-132372865.51753196</v>
       </c>
       <c r="E125">
-        <v>-194024325</v>
+        <v>207070867.1083677</v>
+      </c>
+      <c r="F125">
+        <v>455755.86165350676</v>
+      </c>
+      <c r="G125">
+        <v>-207632029.8616535</v>
       </c>
     </row>
     <row r="126">
@@ -6190,9 +7284,15 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
       <c r="B126">
-        <v>-1736390</v>
-      </c>
-      <c r="E126">
+        <v>1389107.0017844492</v>
+      </c>
+      <c r="C126">
+        <v>-1858170.0017844492</v>
+      </c>
+      <c r="F126">
+        <v>0</v>
+      </c>
+      <c r="G126">
         <v>0</v>
       </c>
     </row>
@@ -6201,16 +7301,25 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>137535576</v>
+        <v>34565545.89108136</v>
       </c>
       <c r="C127">
-        <v>5394929.1021011025</v>
+        <v>147181498.10891864</v>
+      </c>
+      <c r="D127">
+        <v>5773297.13905181</v>
       </c>
       <c r="E127">
-        <v>-194024325</v>
+        <v>68823695.8926312</v>
       </c>
       <c r="F127">
-        <v>41580738.744677514</v>
+        <v>455755.86165350676</v>
+      </c>
+      <c r="G127">
+        <v>-207632029.8616535</v>
+      </c>
+      <c r="H127">
+        <v>44496962.88702199</v>
       </c>
     </row>
     <row r="128">
@@ -6218,10 +7327,16 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>86895461</v>
-      </c>
-      <c r="E128">
-        <v>236451662</v>
+        <v>246.46088694036007</v>
+      </c>
+      <c r="C128">
+        <v>92989788.53911306</v>
+      </c>
+      <c r="F128">
+        <v>-386.3384815454483</v>
+      </c>
+      <c r="G128">
+        <v>253034966.33848155</v>
       </c>
     </row>
     <row r="129">
@@ -6229,22 +7344,28 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>204310994</v>
-      </c>
-      <c r="E129">
-        <v>26323317</v>
+        <v>32515667.743489325</v>
+      </c>
+      <c r="C129">
+        <v>218640144.25651067</v>
+      </c>
+      <c r="F129">
+        <v>-3295294.9014234245</v>
+      </c>
+      <c r="G129">
+        <v>28169476.901423424</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -6255,6 +7376,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6262,27 +7385,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -6296,22 +7425,25 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>-122942467.55551001</v>
+        <v>22018327.74471736</v>
       </c>
       <c r="C3">
-        <v>-96275191.55551001</v>
+        <v>-131564916.38226816</v>
       </c>
       <c r="D3">
-        <v>2054874.200166747</v>
-      </c>
-      <c r="F3">
-        <v>39657659.89161238</v>
+        <v>-103027357.25528264</v>
+      </c>
+      <c r="E3">
+        <v>2198990.7775273025</v>
       </c>
       <c r="H3">
-        <v>664130208.905412</v>
-      </c>
-      <c r="I3">
-        <v>307421796.0234044</v>
+        <v>42439010.793407276</v>
+      </c>
+      <c r="J3">
+        <v>710708326.7393131</v>
+      </c>
+      <c r="K3">
+        <v>328982520.7847246</v>
       </c>
     </row>
     <row r="4">
@@ -6319,22 +7451,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>110005743.8558541</v>
+        <v>68448103.70755324</v>
       </c>
       <c r="C4">
-        <v>91017416.8558541</v>
+        <v>117720888.31249435</v>
       </c>
       <c r="D4">
-        <v>99638967.15497728</v>
-      </c>
-      <c r="F4">
-        <v>97220097.55266985</v>
+        <v>97400833.70755324</v>
+      </c>
+      <c r="E4">
+        <v>106627047.9420895</v>
       </c>
       <c r="H4">
-        <v>336028591.9079875</v>
-      </c>
-      <c r="I4">
-        <v>260604318.24682188</v>
+        <v>104038533.30353715</v>
+      </c>
+      <c r="J4">
+        <v>359595626.1123889</v>
+      </c>
+      <c r="K4">
+        <v>278881545.33355534</v>
       </c>
     </row>
     <row r="5">
@@ -6342,22 +7477,25 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>163811221.91472936</v>
+        <v>198040708.62710348</v>
       </c>
       <c r="C5">
-        <v>170485986.91472936</v>
+        <v>175299960.5604763</v>
       </c>
       <c r="D5">
-        <v>61707334.64182797</v>
-      </c>
-      <c r="F5">
-        <v>156963185.4524271</v>
+        <v>182442853.62710348</v>
+      </c>
+      <c r="E5">
+        <v>66035117.75667858</v>
       </c>
       <c r="H5">
-        <v>409510620.665386</v>
-      </c>
-      <c r="I5">
-        <v>214635860.09236538</v>
+        <v>167971643.8082627</v>
+      </c>
+      <c r="J5">
+        <v>438231244.55482423</v>
+      </c>
+      <c r="K5">
+        <v>229689134.6591707</v>
       </c>
     </row>
     <row r="6">
@@ -6365,22 +7503,25 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>35981568.44635971</v>
+        <v>37107631.57467408</v>
       </c>
       <c r="C6">
-        <v>35683899.44635971</v>
+        <v>38505100.296695724</v>
       </c>
       <c r="D6">
-        <v>48758697.08700663</v>
-      </c>
-      <c r="F6">
-        <v>20552833.37081907</v>
+        <v>38186554.57467408</v>
+      </c>
+      <c r="E6">
+        <v>52178340.26524602</v>
       </c>
       <c r="H6">
-        <v>12128009.921795627</v>
-      </c>
-      <c r="I6">
-        <v>7940905.153190073</v>
+        <v>21994286.08856902</v>
+      </c>
+      <c r="J6">
+        <v>12978595.947929207</v>
+      </c>
+      <c r="K6">
+        <v>8497832.711932998</v>
       </c>
     </row>
     <row r="7">
@@ -6388,22 +7529,25 @@
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B7">
-        <v>4802114.886250772</v>
+        <v>5277095.102937788</v>
       </c>
       <c r="C7">
-        <v>12034833.886250772</v>
+        <v>5138906.482272834</v>
       </c>
       <c r="D7">
-        <v>6170346.995961717</v>
-      </c>
-      <c r="F7">
-        <v>2528499.148221192</v>
+        <v>12878885.102937788</v>
+      </c>
+      <c r="E7">
+        <v>6603098.202878878</v>
       </c>
       <c r="H7">
-        <v>4570102.25856392</v>
-      </c>
-      <c r="I7">
-        <v>1411603.7884611553</v>
+        <v>2705832.94465077</v>
+      </c>
+      <c r="J7">
+        <v>4890621.877545272</v>
+      </c>
+      <c r="K7">
+        <v>1510605.2293112723</v>
       </c>
     </row>
     <row r="8">
@@ -6411,22 +7555,25 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>7897345.730900688</v>
+        <v>29023493.313474886</v>
       </c>
       <c r="C8">
-        <v>5478961.730900688</v>
+        <v>8451218.292480458</v>
       </c>
       <c r="D8">
-        <v>7121459.373437265</v>
-      </c>
-      <c r="F8">
-        <v>5881677.683425967</v>
+        <v>5863223.313474888</v>
+      </c>
+      <c r="E8">
+        <v>7620915.909817383</v>
       </c>
       <c r="H8">
-        <v>4191467.942001269</v>
-      </c>
-      <c r="I8">
-        <v>7880200.371254486</v>
+        <v>6294183.352534386</v>
+      </c>
+      <c r="J8">
+        <v>4485432.416258997</v>
+      </c>
+      <c r="K8">
+        <v>8432870.459928798</v>
       </c>
     </row>
     <row r="9">
@@ -6449,22 +7596,25 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>7115585.91624619</v>
+        <v>6037924.685500602</v>
       </c>
       <c r="C12">
-        <v>5825443.91624619</v>
+        <v>7614630.52349333</v>
       </c>
       <c r="D12">
-        <v>8455127.971632417</v>
-      </c>
-      <c r="F12">
-        <v>2490677.642644719</v>
+        <v>6234005.685500602</v>
+      </c>
+      <c r="E12">
+        <v>9048120.041082911</v>
       </c>
       <c r="H12">
-        <v>901301.7737537245</v>
-      </c>
-      <c r="I12">
-        <v>774900.6955009719</v>
+        <v>2665358.865046231</v>
+      </c>
+      <c r="J12">
+        <v>964513.6856030532</v>
+      </c>
+      <c r="K12">
+        <v>829247.5922700614</v>
       </c>
     </row>
     <row r="13">
@@ -6507,47 +7657,53 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>118863942.74702251</v>
+        <v>119525668.2399662</v>
       </c>
       <c r="C20">
-        <v>118849056.74702251</v>
+        <v>127200348.25490901</v>
       </c>
       <c r="D20">
-        <v>136720356.3766901</v>
-      </c>
-      <c r="F20">
-        <v>79768354.73445517</v>
+        <v>127184418.2399662</v>
+      </c>
+      <c r="E20">
+        <v>146309103.86056402</v>
       </c>
       <c r="H20">
-        <v>216247912.35827166</v>
-      </c>
-      <c r="I20">
-        <v>164405673.14896113</v>
+        <v>85362829.69797404</v>
+      </c>
+      <c r="J20">
+        <v>231414246.62239075</v>
+      </c>
+      <c r="K20">
+        <v>175936103.04630795</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="D21">
-        <v>-202721466.298167</v>
-      </c>
-      <c r="H21">
-        <v>226614774.93214035</v>
-      </c>
-      <c r="I21">
-        <v>32222575.834575552</v>
+      <c r="E21">
+        <v>-216939136.59547168</v>
+      </c>
+      <c r="J21">
+        <v>242508178.8884051</v>
+      </c>
+      <c r="K21">
+        <v>34482474.44182056</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C22">
-        <v>633123.4200582264</v>
-      </c>
-      <c r="F22">
-        <v>-696175.4022089605</v>
+      <c r="B22">
+        <v>41559.90730732796</v>
+      </c>
+      <c r="D22">
+        <v>677526.907307328</v>
+      </c>
+      <c r="H22">
+        <v>-745000.9781010682</v>
       </c>
     </row>
     <row r="23">
@@ -6580,22 +7736,25 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-269805823.8227396</v>
+        <v>-106517754.1118511</v>
       </c>
       <c r="C28">
-        <v>-256576118.8227396</v>
+        <v>-288728389.43679404</v>
       </c>
       <c r="D28">
-        <v>-53681988.603260815</v>
-      </c>
-      <c r="F28">
-        <v>-89769793.55837296</v>
+        <v>-274570832.1118511</v>
+      </c>
+      <c r="E28">
+        <v>-57446921.98107219</v>
       </c>
       <c r="H28">
-        <v>-81409003.66796154</v>
-      </c>
-      <c r="I28">
-        <v>-167818382.31578287</v>
+        <v>-96065709.57938685</v>
+      </c>
+      <c r="J28">
+        <v>-87118543.92790002</v>
+      </c>
+      <c r="K28">
+        <v>-179588159.20800146</v>
       </c>
     </row>
     <row r="29">
@@ -6613,30 +7772,33 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>-276156949.7056806</v>
+        <v>-388770266.3331455</v>
       </c>
       <c r="C31">
-        <v>-298302709.7056806</v>
+        <v>-295524945.275769</v>
       </c>
       <c r="D31">
-        <v>-93126187.52678388</v>
-      </c>
-      <c r="F31">
-        <v>146253125.45300764</v>
+        <v>-319223876.3331455</v>
+      </c>
+      <c r="E31">
+        <v>-99657500.93171632</v>
       </c>
       <c r="H31">
-        <v>-405071366.29054576</v>
-      </c>
-      <c r="I31">
-        <v>-720140049.0030593</v>
+        <v>156510444.30340907</v>
+      </c>
+      <c r="J31">
+        <v>-433480647.4484031</v>
+      </c>
+      <c r="K31">
+        <v>-770646361.7856979</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklarda Azalış (Artış)</v>
       </c>
-      <c r="H32">
-        <v>-296723.3014596442</v>
+      <c r="J32">
+        <v>-317533.69784596475</v>
       </c>
     </row>
     <row r="33">
@@ -6644,16 +7806,19 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-3034002.172029699</v>
+        <v>-4221543.8387419</v>
       </c>
       <c r="C33">
-        <v>-4574309.172029699</v>
-      </c>
-      <c r="F33">
-        <v>-293552.9855572346</v>
-      </c>
-      <c r="I33">
-        <v>-692902.747056664</v>
+        <v>-3246788.9249618165</v>
+      </c>
+      <c r="D33">
+        <v>-4895123.8387419</v>
+      </c>
+      <c r="H33">
+        <v>-314141.0349614528</v>
+      </c>
+      <c r="K33">
+        <v>-741498.7985042133</v>
       </c>
     </row>
     <row r="34">
@@ -6676,22 +7841,25 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>-58140026.11133307</v>
+        <v>-60737462.13049716</v>
       </c>
       <c r="C37">
-        <v>-274823295.1113331</v>
+        <v>-62217619.55726749</v>
       </c>
       <c r="D37">
-        <v>-348600747.57175994</v>
-      </c>
-      <c r="F37">
-        <v>905861.9226949204</v>
+        <v>-294097756.13049716</v>
+      </c>
+      <c r="E37">
+        <v>-373049517.52629155</v>
       </c>
       <c r="H37">
-        <v>29070643.582796175</v>
-      </c>
-      <c r="I37">
-        <v>194484320.9287936</v>
+        <v>969393.6560971239</v>
+      </c>
+      <c r="J37">
+        <v>31109484.527162362</v>
+      </c>
+      <c r="K37">
+        <v>208124287.15167895</v>
       </c>
     </row>
     <row r="38">
@@ -6704,13 +7872,16 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>3797202.496207885</v>
+        <v>3305065.8540071202</v>
       </c>
       <c r="C39">
-        <v>-4023192.503792115</v>
-      </c>
-      <c r="F39">
-        <v>-1090871.4788936414</v>
+        <v>4063515.5518947477</v>
+      </c>
+      <c r="D39">
+        <v>-4305355.14599288</v>
+      </c>
+      <c r="H39">
+        <v>-1167378.675229875</v>
       </c>
     </row>
     <row r="40">
@@ -6718,22 +7889,25 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>140562767.06650496</v>
+        <v>338564388.9562534</v>
       </c>
       <c r="C40">
-        <v>341652335.066505</v>
+        <v>150420998.23818082</v>
       </c>
       <c r="D40">
-        <v>436336738.91164446</v>
-      </c>
-      <c r="F40">
-        <v>-201476886.76805344</v>
+        <v>365613784.9562534</v>
+      </c>
+      <c r="E40">
+        <v>466938786.17250216</v>
       </c>
       <c r="H40">
-        <v>240145769.03654376</v>
-      </c>
-      <c r="I40">
-        <v>344578659.89169776</v>
+        <v>-215607269.7062982</v>
+      </c>
+      <c r="J40">
+        <v>256988155.9322286</v>
+      </c>
+      <c r="K40">
+        <v>368745344.6897524</v>
       </c>
     </row>
     <row r="41">
@@ -6746,13 +7920,16 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>-11305426.31233654</v>
+        <v>802646.907793971</v>
       </c>
       <c r="C42">
-        <v>1131308.6876634595</v>
-      </c>
-      <c r="F42">
-        <v>564830.1277224257</v>
+        <v>-12098321.24751257</v>
+      </c>
+      <c r="D42">
+        <v>1210651.907793971</v>
+      </c>
+      <c r="H42">
+        <v>604443.9322029558</v>
       </c>
     </row>
     <row r="43">
@@ -6765,22 +7942,25 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>-55356220.49897122</v>
+        <v>5352921.200957919</v>
       </c>
       <c r="C44">
-        <v>411707.50102878024</v>
+        <v>-59238574.481167085</v>
       </c>
       <c r="D44">
-        <v>320452.80236889806</v>
-      </c>
-      <c r="F44">
-        <v>228260.54412940718</v>
+        <v>440582.20095791825</v>
+      </c>
+      <c r="E44">
+        <v>342927.4439208053</v>
       </c>
       <c r="H44">
-        <v>-400276.31685862027</v>
-      </c>
-      <c r="I44">
-        <v>467201.78459647053</v>
+        <v>244269.37248674541</v>
+      </c>
+      <c r="J44">
+        <v>-428349.30194913305</v>
+      </c>
+      <c r="K44">
+        <v>499968.52142509545</v>
       </c>
     </row>
     <row r="45">
@@ -6798,13 +7978,16 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
-        <v>-12763417.296877801</v>
+        <v>873050.7393386774</v>
       </c>
       <c r="C47">
-        <v>-8237999.296877801</v>
-      </c>
-      <c r="F47">
-        <v>-30491594.356080335</v>
+        <v>-13658566.993195705</v>
+      </c>
+      <c r="D47">
+        <v>-8815763.260661323</v>
+      </c>
+      <c r="H47">
+        <v>-32630092.282867614</v>
       </c>
     </row>
     <row r="48">
@@ -6812,16 +7995,19 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>2590248.7117764745</v>
+        <v>-1686555.4678175356</v>
       </c>
       <c r="C48">
-        <v>-9809964.288223526</v>
-      </c>
-      <c r="F48">
-        <v>-4368966.017342702</v>
-      </c>
-      <c r="I48">
-        <v>13514559.301209208</v>
+        <v>2771913.253004142</v>
+      </c>
+      <c r="D48">
+        <v>-10497976.467817536</v>
+      </c>
+      <c r="H48">
+        <v>-4675379.144225597</v>
+      </c>
+      <c r="K48">
+        <v>14462389.60190047</v>
       </c>
     </row>
     <row r="49">
@@ -6829,13 +8015,16 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>4011141.9478438348</v>
+        <v>159971058.22280562</v>
       </c>
       <c r="C49">
-        <v>4927284.94784383</v>
-      </c>
-      <c r="F49">
-        <v>164413489.44672397</v>
+        <v>4292459.436176583</v>
+      </c>
+      <c r="D49">
+        <v>5272855.222805625</v>
+      </c>
+      <c r="H49">
+        <v>175944467.53241298</v>
       </c>
     </row>
     <row r="50">
@@ -6863,22 +8052,25 @@
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
       <c r="B54">
-        <v>-125942437.55492093</v>
+        <v>-136876412.87050176</v>
       </c>
       <c r="C54">
-        <v>-100273602.55492093</v>
+        <v>-134775286.3217165</v>
       </c>
       <c r="D54">
-        <v>-116491259.46761262</v>
-      </c>
-      <c r="F54">
-        <v>-121298126.33184494</v>
+        <v>-107306192.87050177</v>
+      </c>
+      <c r="E54">
+        <v>-124661259.17150322</v>
       </c>
       <c r="H54">
-        <v>-187326919.57062724</v>
-      </c>
-      <c r="I54">
-        <v>-159335754.79732603</v>
+        <v>-129805250.9070512</v>
+      </c>
+      <c r="J54">
+        <v>-200464908.50144714</v>
+      </c>
+      <c r="K54">
+        <v>-170510610.9664729</v>
       </c>
     </row>
     <row r="55">
@@ -6921,19 +8113,22 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
       <c r="B62">
-        <v>-1011171.9484329243</v>
+        <v>-1076317.6075865072</v>
       </c>
       <c r="C62">
-        <v>-928873.9484329243</v>
+        <v>-1082089.496728265</v>
       </c>
       <c r="D62">
-        <v>-1609952.660650508</v>
-      </c>
-      <c r="F62">
-        <v>-3457703.2232666546</v>
+        <v>-994019.6075865072</v>
+      </c>
+      <c r="E62">
+        <v>-1722865.1042184262</v>
       </c>
       <c r="H62">
-        <v>-7013980.052193166</v>
+        <v>-3700205.8319545123</v>
+      </c>
+      <c r="J62">
+        <v>-7505898.6322772335</v>
       </c>
     </row>
     <row r="63">
@@ -6957,22 +8152,25 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-314232922.0164377</v>
+        <v>-368743259.842968</v>
       </c>
       <c r="C67">
-        <v>-66668846.01643772</v>
+        <v>-336271338.38827497</v>
       </c>
       <c r="D67">
-        <v>-71937476.37953594</v>
-      </c>
-      <c r="F67">
-        <v>-5614968.393156264</v>
+        <v>-71344599.84296802</v>
+      </c>
+      <c r="E67">
+        <v>-76982740.40539917</v>
       </c>
       <c r="H67">
-        <v>-1976925.8048362632</v>
-      </c>
-      <c r="I67">
-        <v>-5110237.815246438</v>
+        <v>-6008768.668980356</v>
+      </c>
+      <c r="J67">
+        <v>-2115575.5482929084</v>
+      </c>
+      <c r="K67">
+        <v>-5468639.309300004</v>
       </c>
     </row>
     <row r="68">
@@ -7004,10 +8202,10 @@
       <c r="A73" t="str">
         <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
       </c>
-      <c r="C73">
-        <v>-7246648.887022002</v>
-      </c>
-      <c r="F73">
+      <c r="D73">
+        <v>-7754885.466588122</v>
+      </c>
+      <c r="H73">
         <v>0</v>
       </c>
     </row>
@@ -7026,12 +8224,15 @@
         <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
       <c r="B76">
-        <v>-263263332.88341343</v>
+        <v>-297990414.4477371</v>
       </c>
       <c r="C76">
-        <v>-6194562.883413444</v>
-      </c>
-      <c r="F76">
+        <v>-281727047.3417564</v>
+      </c>
+      <c r="D76">
+        <v>-6629012.447737111</v>
+      </c>
+      <c r="H76">
         <v>0</v>
       </c>
     </row>
@@ -7039,11 +8240,14 @@
       <c r="A77" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C77">
-        <v>0</v>
-      </c>
-      <c r="F77">
-        <v>696175.4022089605</v>
+      <c r="B77">
+        <v>-16139</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>745000.9781010682</v>
       </c>
     </row>
     <row r="78">
@@ -7051,19 +8255,22 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-43722940.24600227</v>
+        <v>-62981820.92864279</v>
       </c>
       <c r="C78">
-        <v>-53227634.24600227</v>
+        <v>-46789405.57993043</v>
       </c>
       <c r="D78">
-        <v>-58607128.82854516</v>
-      </c>
-      <c r="F78">
-        <v>-6311143.795365224</v>
-      </c>
-      <c r="I78">
-        <v>-5110237.815246438</v>
+        <v>-56960701.92864279</v>
+      </c>
+      <c r="E78">
+        <v>-62717482.06331481</v>
+      </c>
+      <c r="H78">
+        <v>-6753769.647081424</v>
+      </c>
+      <c r="K78">
+        <v>-5468639.309300004</v>
       </c>
     </row>
     <row r="79">
@@ -7177,22 +8384,25 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>646675716.1512321</v>
+        <v>603639040.6890864</v>
       </c>
       <c r="C101">
-        <v>39148073.151232116</v>
+        <v>692029680.3337355</v>
       </c>
       <c r="D101">
-        <v>-5231669.387558453</v>
-      </c>
-      <c r="F101">
-        <v>-207197573.80718696</v>
+        <v>41893684.68908639</v>
+      </c>
+      <c r="E101">
+        <v>-5598587.365289554</v>
       </c>
       <c r="H101">
-        <v>-37572248.97978582</v>
-      </c>
-      <c r="I101">
-        <v>-66305750.75952724</v>
+        <v>-221729171.4943268</v>
+      </c>
+      <c r="J101">
+        <v>-40207341.642035715</v>
+      </c>
+      <c r="K101">
+        <v>-70956039.25797199</v>
       </c>
     </row>
     <row r="102">
@@ -7219,16 +8429,16 @@
       <c r="A106" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
-      <c r="I106">
-        <v>-91668184.44293045</v>
+      <c r="K106">
+        <v>-98097242.23814769</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="I107">
-        <v>30196487.574600086</v>
+      <c r="K107">
+        <v>32314288.47803704</v>
       </c>
     </row>
     <row r="108">
@@ -7241,30 +8451,33 @@
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B109">
-        <v>41891712.51024938</v>
+        <v>-1012546.993776083</v>
       </c>
       <c r="C109">
-        <v>142697855.51024938</v>
-      </c>
-      <c r="I109">
-        <v>-4834053.891196885</v>
+        <v>44829746.49123971</v>
+      </c>
+      <c r="D109">
+        <v>152705829.00622392</v>
+      </c>
+      <c r="K109">
+        <v>-5173085.497861332</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
-      <c r="D110">
-        <v>-96559669.36048858</v>
-      </c>
-      <c r="F110">
-        <v>-85419028.52160154</v>
+      <c r="E110">
+        <v>-103331786.63081732</v>
       </c>
       <c r="H110">
-        <v>114968039.87145227</v>
-      </c>
-      <c r="I110">
-        <v>-4632334.4262935165</v>
+        <v>-91409807.92357147</v>
+      </c>
+      <c r="J110">
+        <v>123031210.06979486</v>
+      </c>
+      <c r="K110">
+        <v>-4957218.637041211</v>
       </c>
     </row>
     <row r="111">
@@ -7282,13 +8495,16 @@
         <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B113">
-        <v>-24243243.280323405</v>
+        <v>-8496652.259355076</v>
       </c>
       <c r="C113">
-        <v>-24491040.280323405</v>
-      </c>
-      <c r="F113">
-        <v>-13339154.228591269</v>
+        <v>-25943519.260914527</v>
+      </c>
+      <c r="D113">
+        <v>-26208695.259355076</v>
+      </c>
+      <c r="H113">
+        <v>-14274682.66734114</v>
       </c>
     </row>
     <row r="114">
@@ -7311,16 +8527,19 @@
         <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
       <c r="B117">
-        <v>568.6145389527082</v>
+        <v>-16999181.81174603</v>
       </c>
       <c r="C117">
-        <v>-78520336.38546105</v>
-      </c>
-      <c r="F117">
-        <v>-108439391.05699414</v>
+        <v>608.493759393692</v>
+      </c>
+      <c r="D117">
+        <v>-84027282.81174603</v>
       </c>
       <c r="H117">
-        <v>-152263986.08160803</v>
+        <v>-116044680.9034142</v>
+      </c>
+      <c r="J117">
+        <v>-162942870.7196937</v>
       </c>
     </row>
     <row r="118">
@@ -7328,12 +8547,15 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
-        <v>-2739757.6932328176</v>
+        <v>-17684797.24603642</v>
       </c>
       <c r="C118">
-        <v>-538405.6932328173</v>
-      </c>
-      <c r="F118">
+        <v>-2931907.8995636823</v>
+      </c>
+      <c r="D118">
+        <v>-576166.2460364214</v>
+      </c>
+      <c r="H118">
         <v>0</v>
       </c>
     </row>
@@ -7372,13 +8594,16 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>209500326.57928437</v>
+        <v>256914108.59083575</v>
       </c>
       <c r="C125">
-        <v>-123795964.42071562</v>
-      </c>
-      <c r="F125">
-        <v>-173154882.30873084</v>
+        <v>224193425.5631923</v>
+      </c>
+      <c r="D125">
+        <v>-132478272.40916426</v>
+      </c>
+      <c r="H125">
+        <v>-185298929.3698999</v>
       </c>
     </row>
     <row r="126">
@@ -7386,12 +8611,15 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
       <c r="B126">
-        <v>-1830778.7006349126</v>
+        <v>-570071.5591527291</v>
       </c>
       <c r="C126">
-        <v>-94388.7006349125</v>
-      </c>
-      <c r="F126">
+        <v>-1959178.5609371783</v>
+      </c>
+      <c r="D126">
+        <v>-101008.55915272905</v>
+      </c>
+      <c r="H126">
         <v>0</v>
       </c>
     </row>
@@ -7400,22 +8628,25 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>207669547.87864947</v>
+        <v>256344037.03168303</v>
       </c>
       <c r="C127">
-        <v>-123890353.12135053</v>
+        <v>222234247.00225514</v>
       </c>
       <c r="D127">
-        <v>-87704543.47877412</v>
-      </c>
-      <c r="F127">
-        <v>-173154882.30873084</v>
+        <v>-132579280.96831699</v>
+      </c>
+      <c r="E127">
+        <v>-93855615.22034681</v>
       </c>
       <c r="H127">
-        <v>430240134.49796945</v>
-      </c>
-      <c r="I127">
-        <v>76670052.65130469</v>
+        <v>-185298929.3698999</v>
+      </c>
+      <c r="J127">
+        <v>460414602.41526014</v>
+      </c>
+      <c r="K127">
+        <v>82047231.2509797</v>
       </c>
     </row>
     <row r="128">
@@ -7423,13 +8654,16 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>86894366.22610682</v>
+        <v>92989249.78370005</v>
       </c>
       <c r="C128">
-        <v>236450567.22610682</v>
-      </c>
-      <c r="F128">
-        <v>496538925.0880824</v>
+        <v>92988616.98433156</v>
+      </c>
+      <c r="D128">
+        <v>253033794.78370005</v>
+      </c>
+      <c r="H128">
+        <v>531363193.3591938</v>
       </c>
     </row>
     <row r="129">
@@ -7437,18 +8671,21 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>264883299.13542902</v>
+        <v>319271590.97561663</v>
       </c>
       <c r="C129">
-        <v>86895622.13542902</v>
-      </c>
-      <c r="F129">
-        <v>236450567.22610682</v>
+        <v>283460628.33070385</v>
+      </c>
+      <c r="D129">
+        <v>92989960.97561663</v>
+      </c>
+      <c r="H129">
+        <v>253033794.78370005</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>